--- a/data/pokemon_data.xlsx
+++ b/data/pokemon_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanaka\Desktop\Python\PokemonAutoCapture\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tanaka\Desktop\Python\PokemonAutoCapture\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFC8CF4-CA69-47C2-BF55-2A23891B4A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF9A580-014D-4C06-B53F-57DD7B2C4FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17280" yWindow="0" windowWidth="11520" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="945">
   <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>image</t>
-  </si>
-  <si>
     <t>background.svg</t>
   </si>
   <si>
@@ -2855,6 +2849,14 @@
   </si>
   <si>
     <t>pokemon</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>image_name</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>label</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3242,19 +3244,20 @@
   <dimension ref="A1:C943"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="1" max="1" width="21.75" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="32.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>944</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>943</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
@@ -3262,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
@@ -3270,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
@@ -3278,7 +3281,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
@@ -3286,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
@@ -3294,7 +3297,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
@@ -3302,7 +3305,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
@@ -3310,7 +3313,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
@@ -3318,7 +3321,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
@@ -3326,7 +3329,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
@@ -3334,7 +3337,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.15">
@@ -3342,7 +3345,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.15">
@@ -3350,7 +3353,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.15">
@@ -3358,7 +3361,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.15">
@@ -3366,7 +3369,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.15">
@@ -3374,7 +3377,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.15">
@@ -3382,7 +3385,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.15">
@@ -3390,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.15">
@@ -3398,7 +3401,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.15">
@@ -3406,7 +3409,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.15">
@@ -3414,7 +3417,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.15">
@@ -3422,7 +3425,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.15">
@@ -3430,7 +3433,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.15">
@@ -3438,7 +3441,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.15">
@@ -3446,7 +3449,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.15">
@@ -3454,7 +3457,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.15">
@@ -3462,7 +3465,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.15">
@@ -3470,7 +3473,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.15">
@@ -3478,7 +3481,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.15">
@@ -3486,7 +3489,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.15">
@@ -3494,7 +3497,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.15">
@@ -3502,7 +3505,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.15">
@@ -3510,7 +3513,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.15">
@@ -3518,7 +3521,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.15">
@@ -3526,7 +3529,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.15">
@@ -3534,7 +3537,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.15">
@@ -3542,7 +3545,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.15">
@@ -3550,7 +3553,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.15">
@@ -3558,7 +3561,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.15">
@@ -3566,7 +3569,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.15">
@@ -3574,7 +3577,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.15">
@@ -3582,7 +3585,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.15">
@@ -3590,7 +3593,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.15">
@@ -3598,7 +3601,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.15">
@@ -3606,7 +3609,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.15">
@@ -3614,7 +3617,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.15">
@@ -3622,7 +3625,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.15">
@@ -3630,7 +3633,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.15">
@@ -3638,7 +3641,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.15">
@@ -3646,7 +3649,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.15">
@@ -3654,7 +3657,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.15">
@@ -3662,7 +3665,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.15">
@@ -3670,7 +3673,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.15">
@@ -3678,7 +3681,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.15">
@@ -3686,7 +3689,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.15">
@@ -3694,7 +3697,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.15">
@@ -3702,7 +3705,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.15">
@@ -3710,7 +3713,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.15">
@@ -3718,7 +3721,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.15">
@@ -3726,7 +3729,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.15">
@@ -3734,7 +3737,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.15">
@@ -3742,7 +3745,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.15">
@@ -3750,7 +3753,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.15">
@@ -3758,7 +3761,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.15">
@@ -3766,7 +3769,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.15">
@@ -3774,7 +3777,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.15">
@@ -3782,7 +3785,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.15">
@@ -3790,7 +3793,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.15">
@@ -3798,7 +3801,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.15">
@@ -3806,7 +3809,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.15">
@@ -3814,7 +3817,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.15">
@@ -3822,7 +3825,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.15">
@@ -3830,7 +3833,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.15">
@@ -3838,7 +3841,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.15">
@@ -3846,7 +3849,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.15">
@@ -3854,7 +3857,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.15">
@@ -3862,7 +3865,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.15">
@@ -3870,7 +3873,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.15">
@@ -3878,7 +3881,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.15">
@@ -3886,7 +3889,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
@@ -3894,7 +3897,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.15">
@@ -3902,7 +3905,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.15">
@@ -3910,7 +3913,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
@@ -3918,7 +3921,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
@@ -3926,7 +3929,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
@@ -3934,7 +3937,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.15">
@@ -3942,7 +3945,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.15">
@@ -3950,7 +3953,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.15">
@@ -3958,7 +3961,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.15">
@@ -3966,7 +3969,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.15">
@@ -3974,7 +3977,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.15">
@@ -3982,7 +3985,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.15">
@@ -3990,7 +3993,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.15">
@@ -3998,7 +4001,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.15">
@@ -4006,7 +4009,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.15">
@@ -4014,7 +4017,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.15">
@@ -4022,7 +4025,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.15">
@@ -4030,7 +4033,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.15">
@@ -4038,7 +4041,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.15">
@@ -4046,7 +4049,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.15">
@@ -4054,7 +4057,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.15">
@@ -4062,7 +4065,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.15">
@@ -4070,7 +4073,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.15">
@@ -4078,7 +4081,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.15">
@@ -4086,7 +4089,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.15">
@@ -4094,7 +4097,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.15">
@@ -4102,7 +4105,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.15">
@@ -4110,7 +4113,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.15">
@@ -4118,7 +4121,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.15">
@@ -4126,7 +4129,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.15">
@@ -4134,7 +4137,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.15">
@@ -4142,7 +4145,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.15">
@@ -4150,7 +4153,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.15">
@@ -4158,7 +4161,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.15">
@@ -4166,7 +4169,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.15">
@@ -4174,7 +4177,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.15">
@@ -4182,7 +4185,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.15">
@@ -4190,7 +4193,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.15">
@@ -4198,7 +4201,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.15">
@@ -4206,7 +4209,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.15">
@@ -4214,7 +4217,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.15">
@@ -4222,7 +4225,7 @@
         <v>120</v>
       </c>
       <c r="C122" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.15">
@@ -4230,7 +4233,7 @@
         <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.15">
@@ -4238,7 +4241,7 @@
         <v>122</v>
       </c>
       <c r="C124" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.15">
@@ -4246,7 +4249,7 @@
         <v>123</v>
       </c>
       <c r="C125" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.15">
@@ -4254,7 +4257,7 @@
         <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.15">
@@ -4262,7 +4265,7 @@
         <v>125</v>
       </c>
       <c r="C127" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.15">
@@ -4270,7 +4273,7 @@
         <v>126</v>
       </c>
       <c r="C128" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.15">
@@ -4278,7 +4281,7 @@
         <v>127</v>
       </c>
       <c r="C129" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.15">
@@ -4286,7 +4289,7 @@
         <v>128</v>
       </c>
       <c r="C130" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.15">
@@ -4294,7 +4297,7 @@
         <v>129</v>
       </c>
       <c r="C131" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.15">
@@ -4302,7 +4305,7 @@
         <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.15">
@@ -4310,7 +4313,7 @@
         <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.15">
@@ -4318,7 +4321,7 @@
         <v>132</v>
       </c>
       <c r="C134" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.15">
@@ -4326,7 +4329,7 @@
         <v>133</v>
       </c>
       <c r="C135" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.15">
@@ -4334,7 +4337,7 @@
         <v>134</v>
       </c>
       <c r="C136" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.15">
@@ -4342,7 +4345,7 @@
         <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.15">
@@ -4350,7 +4353,7 @@
         <v>136</v>
       </c>
       <c r="C138" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.15">
@@ -4358,7 +4361,7 @@
         <v>137</v>
       </c>
       <c r="C139" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.15">
@@ -4366,7 +4369,7 @@
         <v>138</v>
       </c>
       <c r="C140" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.15">
@@ -4374,7 +4377,7 @@
         <v>139</v>
       </c>
       <c r="C141" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.15">
@@ -4382,7 +4385,7 @@
         <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.15">
@@ -4390,7 +4393,7 @@
         <v>141</v>
       </c>
       <c r="C143" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.15">
@@ -4398,7 +4401,7 @@
         <v>142</v>
       </c>
       <c r="C144" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.15">
@@ -4406,7 +4409,7 @@
         <v>143</v>
       </c>
       <c r="C145" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.15">
@@ -4414,7 +4417,7 @@
         <v>144</v>
       </c>
       <c r="C146" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.15">
@@ -4422,7 +4425,7 @@
         <v>145</v>
       </c>
       <c r="C147" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.15">
@@ -4430,7 +4433,7 @@
         <v>146</v>
       </c>
       <c r="C148" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.15">
@@ -4438,7 +4441,7 @@
         <v>147</v>
       </c>
       <c r="C149" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.15">
@@ -4446,7 +4449,7 @@
         <v>148</v>
       </c>
       <c r="C150" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.15">
@@ -4454,7 +4457,7 @@
         <v>149</v>
       </c>
       <c r="C151" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.15">
@@ -4462,7 +4465,7 @@
         <v>150</v>
       </c>
       <c r="C152" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.15">
@@ -4470,7 +4473,7 @@
         <v>151</v>
       </c>
       <c r="C153" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.15">
@@ -4478,7 +4481,7 @@
         <v>152</v>
       </c>
       <c r="C154" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.15">
@@ -4486,7 +4489,7 @@
         <v>153</v>
       </c>
       <c r="C155" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.15">
@@ -4494,7 +4497,7 @@
         <v>154</v>
       </c>
       <c r="C156" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.15">
@@ -4502,7 +4505,7 @@
         <v>155</v>
       </c>
       <c r="C157" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.15">
@@ -4510,7 +4513,7 @@
         <v>156</v>
       </c>
       <c r="C158" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.15">
@@ -4518,7 +4521,7 @@
         <v>157</v>
       </c>
       <c r="C159" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.15">
@@ -4526,7 +4529,7 @@
         <v>158</v>
       </c>
       <c r="C160" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.15">
@@ -4534,7 +4537,7 @@
         <v>159</v>
       </c>
       <c r="C161" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.15">
@@ -4542,7 +4545,7 @@
         <v>160</v>
       </c>
       <c r="C162" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.15">
@@ -4550,7 +4553,7 @@
         <v>161</v>
       </c>
       <c r="C163" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.15">
@@ -4558,7 +4561,7 @@
         <v>162</v>
       </c>
       <c r="C164" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.15">
@@ -4566,7 +4569,7 @@
         <v>163</v>
       </c>
       <c r="C165" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.15">
@@ -4574,7 +4577,7 @@
         <v>164</v>
       </c>
       <c r="C166" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.15">
@@ -4582,7 +4585,7 @@
         <v>165</v>
       </c>
       <c r="C167" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.15">
@@ -4590,7 +4593,7 @@
         <v>166</v>
       </c>
       <c r="C168" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.15">
@@ -4598,7 +4601,7 @@
         <v>167</v>
       </c>
       <c r="C169" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.15">
@@ -4606,7 +4609,7 @@
         <v>168</v>
       </c>
       <c r="C170" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.15">
@@ -4614,7 +4617,7 @@
         <v>169</v>
       </c>
       <c r="C171" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.15">
@@ -4622,7 +4625,7 @@
         <v>170</v>
       </c>
       <c r="C172" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.15">
@@ -4630,7 +4633,7 @@
         <v>171</v>
       </c>
       <c r="C173" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.15">
@@ -4638,7 +4641,7 @@
         <v>172</v>
       </c>
       <c r="C174" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.15">
@@ -4646,7 +4649,7 @@
         <v>173</v>
       </c>
       <c r="C175" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.15">
@@ -4654,7 +4657,7 @@
         <v>174</v>
       </c>
       <c r="C176" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.15">
@@ -4662,7 +4665,7 @@
         <v>175</v>
       </c>
       <c r="C177" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.15">
@@ -4670,7 +4673,7 @@
         <v>176</v>
       </c>
       <c r="C178" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.15">
@@ -4678,7 +4681,7 @@
         <v>177</v>
       </c>
       <c r="C179" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.15">
@@ -4686,7 +4689,7 @@
         <v>178</v>
       </c>
       <c r="C180" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.15">
@@ -4694,7 +4697,7 @@
         <v>179</v>
       </c>
       <c r="C181" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.15">
@@ -4702,7 +4705,7 @@
         <v>180</v>
       </c>
       <c r="C182" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.15">
@@ -4710,7 +4713,7 @@
         <v>181</v>
       </c>
       <c r="C183" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.15">
@@ -4718,7 +4721,7 @@
         <v>182</v>
       </c>
       <c r="C184" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.15">
@@ -4726,7 +4729,7 @@
         <v>183</v>
       </c>
       <c r="C185" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.15">
@@ -4734,7 +4737,7 @@
         <v>184</v>
       </c>
       <c r="C186" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.15">
@@ -4742,7 +4745,7 @@
         <v>185</v>
       </c>
       <c r="C187" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.15">
@@ -4750,7 +4753,7 @@
         <v>186</v>
       </c>
       <c r="C188" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.15">
@@ -4758,7 +4761,7 @@
         <v>187</v>
       </c>
       <c r="C189" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.15">
@@ -4766,7 +4769,7 @@
         <v>188</v>
       </c>
       <c r="C190" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.15">
@@ -4774,7 +4777,7 @@
         <v>189</v>
       </c>
       <c r="C191" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.15">
@@ -4782,7 +4785,7 @@
         <v>190</v>
       </c>
       <c r="C192" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.15">
@@ -4790,7 +4793,7 @@
         <v>191</v>
       </c>
       <c r="C193" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.15">
@@ -4798,7 +4801,7 @@
         <v>192</v>
       </c>
       <c r="C194" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.15">
@@ -4806,7 +4809,7 @@
         <v>193</v>
       </c>
       <c r="C195" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.15">
@@ -4814,7 +4817,7 @@
         <v>194</v>
       </c>
       <c r="C196" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.15">
@@ -4822,7 +4825,7 @@
         <v>195</v>
       </c>
       <c r="C197" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.15">
@@ -4830,7 +4833,7 @@
         <v>196</v>
       </c>
       <c r="C198" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.15">
@@ -4838,7 +4841,7 @@
         <v>197</v>
       </c>
       <c r="C199" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.15">
@@ -4846,7 +4849,7 @@
         <v>198</v>
       </c>
       <c r="C200" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.15">
@@ -4854,7 +4857,7 @@
         <v>199</v>
       </c>
       <c r="C201" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.15">
@@ -4862,7 +4865,7 @@
         <v>200</v>
       </c>
       <c r="C202" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.15">
@@ -4870,7 +4873,7 @@
         <v>201</v>
       </c>
       <c r="C203" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.15">
@@ -4878,7 +4881,7 @@
         <v>202</v>
       </c>
       <c r="C204" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.15">
@@ -4886,7 +4889,7 @@
         <v>203</v>
       </c>
       <c r="C205" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.15">
@@ -4894,7 +4897,7 @@
         <v>204</v>
       </c>
       <c r="C206" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.15">
@@ -4902,7 +4905,7 @@
         <v>205</v>
       </c>
       <c r="C207" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.15">
@@ -4910,7 +4913,7 @@
         <v>206</v>
       </c>
       <c r="C208" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.15">
@@ -4918,7 +4921,7 @@
         <v>207</v>
       </c>
       <c r="C209" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.15">
@@ -4926,7 +4929,7 @@
         <v>208</v>
       </c>
       <c r="C210" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.15">
@@ -4934,7 +4937,7 @@
         <v>209</v>
       </c>
       <c r="C211" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.15">
@@ -4942,7 +4945,7 @@
         <v>210</v>
       </c>
       <c r="C212" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.15">
@@ -4950,7 +4953,7 @@
         <v>211</v>
       </c>
       <c r="C213" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.15">
@@ -4958,7 +4961,7 @@
         <v>212</v>
       </c>
       <c r="C214" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.15">
@@ -4966,7 +4969,7 @@
         <v>213</v>
       </c>
       <c r="C215" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.15">
@@ -4974,7 +4977,7 @@
         <v>214</v>
       </c>
       <c r="C216" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.15">
@@ -4982,7 +4985,7 @@
         <v>215</v>
       </c>
       <c r="C217" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.15">
@@ -4990,7 +4993,7 @@
         <v>216</v>
       </c>
       <c r="C218" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.15">
@@ -4998,7 +5001,7 @@
         <v>217</v>
       </c>
       <c r="C219" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.15">
@@ -5006,7 +5009,7 @@
         <v>218</v>
       </c>
       <c r="C220" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.15">
@@ -5014,7 +5017,7 @@
         <v>219</v>
       </c>
       <c r="C221" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.15">
@@ -5022,7 +5025,7 @@
         <v>220</v>
       </c>
       <c r="C222" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.15">
@@ -5030,7 +5033,7 @@
         <v>221</v>
       </c>
       <c r="C223" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.15">
@@ -5038,7 +5041,7 @@
         <v>222</v>
       </c>
       <c r="C224" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.15">
@@ -5046,7 +5049,7 @@
         <v>223</v>
       </c>
       <c r="C225" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.15">
@@ -5054,7 +5057,7 @@
         <v>224</v>
       </c>
       <c r="C226" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.15">
@@ -5062,7 +5065,7 @@
         <v>225</v>
       </c>
       <c r="C227" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.15">
@@ -5070,7 +5073,7 @@
         <v>226</v>
       </c>
       <c r="C228" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.15">
@@ -5078,7 +5081,7 @@
         <v>227</v>
       </c>
       <c r="C229" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.15">
@@ -5086,7 +5089,7 @@
         <v>228</v>
       </c>
       <c r="C230" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.15">
@@ -5094,7 +5097,7 @@
         <v>229</v>
       </c>
       <c r="C231" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.15">
@@ -5102,7 +5105,7 @@
         <v>230</v>
       </c>
       <c r="C232" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.15">
@@ -5110,7 +5113,7 @@
         <v>231</v>
       </c>
       <c r="C233" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.15">
@@ -5118,7 +5121,7 @@
         <v>232</v>
       </c>
       <c r="C234" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.15">
@@ -5126,7 +5129,7 @@
         <v>233</v>
       </c>
       <c r="C235" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.15">
@@ -5134,7 +5137,7 @@
         <v>234</v>
       </c>
       <c r="C236" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.15">
@@ -5142,7 +5145,7 @@
         <v>235</v>
       </c>
       <c r="C237" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.15">
@@ -5150,7 +5153,7 @@
         <v>236</v>
       </c>
       <c r="C238" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.15">
@@ -5158,7 +5161,7 @@
         <v>237</v>
       </c>
       <c r="C239" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.15">
@@ -5166,7 +5169,7 @@
         <v>238</v>
       </c>
       <c r="C240" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.15">
@@ -5174,7 +5177,7 @@
         <v>239</v>
       </c>
       <c r="C241" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.15">
@@ -5182,7 +5185,7 @@
         <v>240</v>
       </c>
       <c r="C242" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.15">
@@ -5190,7 +5193,7 @@
         <v>241</v>
       </c>
       <c r="C243" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.15">
@@ -5198,7 +5201,7 @@
         <v>242</v>
       </c>
       <c r="C244" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.15">
@@ -5206,7 +5209,7 @@
         <v>243</v>
       </c>
       <c r="C245" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.15">
@@ -5214,7 +5217,7 @@
         <v>244</v>
       </c>
       <c r="C246" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.15">
@@ -5222,7 +5225,7 @@
         <v>245</v>
       </c>
       <c r="C247" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.15">
@@ -5230,7 +5233,7 @@
         <v>246</v>
       </c>
       <c r="C248" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.15">
@@ -5238,7 +5241,7 @@
         <v>247</v>
       </c>
       <c r="C249" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.15">
@@ -5246,7 +5249,7 @@
         <v>248</v>
       </c>
       <c r="C250" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.15">
@@ -5254,7 +5257,7 @@
         <v>249</v>
       </c>
       <c r="C251" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.15">
@@ -5262,7 +5265,7 @@
         <v>250</v>
       </c>
       <c r="C252" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.15">
@@ -5270,7 +5273,7 @@
         <v>251</v>
       </c>
       <c r="C253" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.15">
@@ -5278,7 +5281,7 @@
         <v>252</v>
       </c>
       <c r="C254" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.15">
@@ -5286,7 +5289,7 @@
         <v>253</v>
       </c>
       <c r="C255" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.15">
@@ -5294,7 +5297,7 @@
         <v>254</v>
       </c>
       <c r="C256" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.15">
@@ -5302,7 +5305,7 @@
         <v>255</v>
       </c>
       <c r="C257" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.15">
@@ -5310,7 +5313,7 @@
         <v>256</v>
       </c>
       <c r="C258" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.15">
@@ -5318,7 +5321,7 @@
         <v>257</v>
       </c>
       <c r="C259" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.15">
@@ -5326,7 +5329,7 @@
         <v>258</v>
       </c>
       <c r="C260" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.15">
@@ -5334,7 +5337,7 @@
         <v>259</v>
       </c>
       <c r="C261" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.15">
@@ -5342,7 +5345,7 @@
         <v>260</v>
       </c>
       <c r="C262" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.15">
@@ -5350,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="C263" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.15">
@@ -5358,7 +5361,7 @@
         <v>262</v>
       </c>
       <c r="C264" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.15">
@@ -5366,7 +5369,7 @@
         <v>263</v>
       </c>
       <c r="C265" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.15">
@@ -5374,7 +5377,7 @@
         <v>264</v>
       </c>
       <c r="C266" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.15">
@@ -5382,7 +5385,7 @@
         <v>265</v>
       </c>
       <c r="C267" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.15">
@@ -5390,7 +5393,7 @@
         <v>266</v>
       </c>
       <c r="C268" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.15">
@@ -5398,7 +5401,7 @@
         <v>267</v>
       </c>
       <c r="C269" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.15">
@@ -5406,7 +5409,7 @@
         <v>268</v>
       </c>
       <c r="C270" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.15">
@@ -5414,7 +5417,7 @@
         <v>269</v>
       </c>
       <c r="C271" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.15">
@@ -5422,7 +5425,7 @@
         <v>270</v>
       </c>
       <c r="C272" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.15">
@@ -5430,7 +5433,7 @@
         <v>271</v>
       </c>
       <c r="C273" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.15">
@@ -5438,7 +5441,7 @@
         <v>272</v>
       </c>
       <c r="C274" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.15">
@@ -5446,7 +5449,7 @@
         <v>273</v>
       </c>
       <c r="C275" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.15">
@@ -5454,7 +5457,7 @@
         <v>274</v>
       </c>
       <c r="C276" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.15">
@@ -5462,7 +5465,7 @@
         <v>275</v>
       </c>
       <c r="C277" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.15">
@@ -5470,7 +5473,7 @@
         <v>276</v>
       </c>
       <c r="C278" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.15">
@@ -5478,7 +5481,7 @@
         <v>277</v>
       </c>
       <c r="C279" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.15">
@@ -5486,7 +5489,7 @@
         <v>278</v>
       </c>
       <c r="C280" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.15">
@@ -5494,7 +5497,7 @@
         <v>279</v>
       </c>
       <c r="C281" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.15">
@@ -5502,7 +5505,7 @@
         <v>280</v>
       </c>
       <c r="C282" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.15">
@@ -5510,7 +5513,7 @@
         <v>281</v>
       </c>
       <c r="C283" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.15">
@@ -5518,7 +5521,7 @@
         <v>282</v>
       </c>
       <c r="C284" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.15">
@@ -5526,7 +5529,7 @@
         <v>283</v>
       </c>
       <c r="C285" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.15">
@@ -5534,7 +5537,7 @@
         <v>284</v>
       </c>
       <c r="C286" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.15">
@@ -5542,7 +5545,7 @@
         <v>285</v>
       </c>
       <c r="C287" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.15">
@@ -5550,7 +5553,7 @@
         <v>286</v>
       </c>
       <c r="C288" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.15">
@@ -5558,7 +5561,7 @@
         <v>287</v>
       </c>
       <c r="C289" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.15">
@@ -5566,7 +5569,7 @@
         <v>288</v>
       </c>
       <c r="C290" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.15">
@@ -5574,7 +5577,7 @@
         <v>289</v>
       </c>
       <c r="C291" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.15">
@@ -5582,7 +5585,7 @@
         <v>290</v>
       </c>
       <c r="C292" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.15">
@@ -5590,7 +5593,7 @@
         <v>291</v>
       </c>
       <c r="C293" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.15">
@@ -5598,7 +5601,7 @@
         <v>292</v>
       </c>
       <c r="C294" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.15">
@@ -5606,7 +5609,7 @@
         <v>293</v>
       </c>
       <c r="C295" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.15">
@@ -5614,7 +5617,7 @@
         <v>294</v>
       </c>
       <c r="C296" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.15">
@@ -5622,7 +5625,7 @@
         <v>295</v>
       </c>
       <c r="C297" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.15">
@@ -5630,7 +5633,7 @@
         <v>296</v>
       </c>
       <c r="C298" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.15">
@@ -5638,7 +5641,7 @@
         <v>297</v>
       </c>
       <c r="C299" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.15">
@@ -5646,7 +5649,7 @@
         <v>298</v>
       </c>
       <c r="C300" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.15">
@@ -5654,7 +5657,7 @@
         <v>299</v>
       </c>
       <c r="C301" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.15">
@@ -5662,7 +5665,7 @@
         <v>300</v>
       </c>
       <c r="C302" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.15">
@@ -5670,7 +5673,7 @@
         <v>301</v>
       </c>
       <c r="C303" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.15">
@@ -5678,7 +5681,7 @@
         <v>302</v>
       </c>
       <c r="C304" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.15">
@@ -5686,7 +5689,7 @@
         <v>303</v>
       </c>
       <c r="C305" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.15">
@@ -5694,7 +5697,7 @@
         <v>304</v>
       </c>
       <c r="C306" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.15">
@@ -5702,7 +5705,7 @@
         <v>305</v>
       </c>
       <c r="C307" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.15">
@@ -5710,7 +5713,7 @@
         <v>306</v>
       </c>
       <c r="C308" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.15">
@@ -5718,7 +5721,7 @@
         <v>307</v>
       </c>
       <c r="C309" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.15">
@@ -5726,7 +5729,7 @@
         <v>308</v>
       </c>
       <c r="C310" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.15">
@@ -5734,7 +5737,7 @@
         <v>309</v>
       </c>
       <c r="C311" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.15">
@@ -5742,7 +5745,7 @@
         <v>310</v>
       </c>
       <c r="C312" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.15">
@@ -5750,7 +5753,7 @@
         <v>311</v>
       </c>
       <c r="C313" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.15">
@@ -5758,7 +5761,7 @@
         <v>312</v>
       </c>
       <c r="C314" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.15">
@@ -5766,7 +5769,7 @@
         <v>313</v>
       </c>
       <c r="C315" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.15">
@@ -5774,7 +5777,7 @@
         <v>314</v>
       </c>
       <c r="C316" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.15">
@@ -5782,7 +5785,7 @@
         <v>315</v>
       </c>
       <c r="C317" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.15">
@@ -5790,7 +5793,7 @@
         <v>316</v>
       </c>
       <c r="C318" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.15">
@@ -5798,7 +5801,7 @@
         <v>317</v>
       </c>
       <c r="C319" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.15">
@@ -5806,7 +5809,7 @@
         <v>318</v>
       </c>
       <c r="C320" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.15">
@@ -5814,7 +5817,7 @@
         <v>319</v>
       </c>
       <c r="C321" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.15">
@@ -5822,7 +5825,7 @@
         <v>320</v>
       </c>
       <c r="C322" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.15">
@@ -5830,7 +5833,7 @@
         <v>321</v>
       </c>
       <c r="C323" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.15">
@@ -5838,7 +5841,7 @@
         <v>322</v>
       </c>
       <c r="C324" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.15">
@@ -5846,7 +5849,7 @@
         <v>323</v>
       </c>
       <c r="C325" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.15">
@@ -5854,7 +5857,7 @@
         <v>324</v>
       </c>
       <c r="C326" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.15">
@@ -5862,7 +5865,7 @@
         <v>325</v>
       </c>
       <c r="C327" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.15">
@@ -5870,7 +5873,7 @@
         <v>326</v>
       </c>
       <c r="C328" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.15">
@@ -5878,7 +5881,7 @@
         <v>327</v>
       </c>
       <c r="C329" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.15">
@@ -5886,7 +5889,7 @@
         <v>328</v>
       </c>
       <c r="C330" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.15">
@@ -5894,7 +5897,7 @@
         <v>329</v>
       </c>
       <c r="C331" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.15">
@@ -5902,7 +5905,7 @@
         <v>330</v>
       </c>
       <c r="C332" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.15">
@@ -5910,7 +5913,7 @@
         <v>331</v>
       </c>
       <c r="C333" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.15">
@@ -5918,7 +5921,7 @@
         <v>332</v>
       </c>
       <c r="C334" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.15">
@@ -5926,7 +5929,7 @@
         <v>333</v>
       </c>
       <c r="C335" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.15">
@@ -5934,7 +5937,7 @@
         <v>334</v>
       </c>
       <c r="C336" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.15">
@@ -5942,7 +5945,7 @@
         <v>335</v>
       </c>
       <c r="C337" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.15">
@@ -5950,7 +5953,7 @@
         <v>336</v>
       </c>
       <c r="C338" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.15">
@@ -5958,7 +5961,7 @@
         <v>337</v>
       </c>
       <c r="C339" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.15">
@@ -5966,7 +5969,7 @@
         <v>338</v>
       </c>
       <c r="C340" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.15">
@@ -5974,7 +5977,7 @@
         <v>339</v>
       </c>
       <c r="C341" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.15">
@@ -5982,7 +5985,7 @@
         <v>340</v>
       </c>
       <c r="C342" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.15">
@@ -5990,7 +5993,7 @@
         <v>341</v>
       </c>
       <c r="C343" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.15">
@@ -5998,7 +6001,7 @@
         <v>342</v>
       </c>
       <c r="C344" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.15">
@@ -6006,7 +6009,7 @@
         <v>343</v>
       </c>
       <c r="C345" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.15">
@@ -6014,7 +6017,7 @@
         <v>344</v>
       </c>
       <c r="C346" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.15">
@@ -6022,7 +6025,7 @@
         <v>345</v>
       </c>
       <c r="C347" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.15">
@@ -6030,7 +6033,7 @@
         <v>346</v>
       </c>
       <c r="C348" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.15">
@@ -6038,7 +6041,7 @@
         <v>347</v>
       </c>
       <c r="C349" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.15">
@@ -6046,7 +6049,7 @@
         <v>348</v>
       </c>
       <c r="C350" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.15">
@@ -6054,7 +6057,7 @@
         <v>349</v>
       </c>
       <c r="C351" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.15">
@@ -6062,7 +6065,7 @@
         <v>350</v>
       </c>
       <c r="C352" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.15">
@@ -6070,7 +6073,7 @@
         <v>351</v>
       </c>
       <c r="C353" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.15">
@@ -6078,7 +6081,7 @@
         <v>352</v>
       </c>
       <c r="C354" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.15">
@@ -6086,7 +6089,7 @@
         <v>353</v>
       </c>
       <c r="C355" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.15">
@@ -6094,7 +6097,7 @@
         <v>354</v>
       </c>
       <c r="C356" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.15">
@@ -6102,7 +6105,7 @@
         <v>355</v>
       </c>
       <c r="C357" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.15">
@@ -6110,7 +6113,7 @@
         <v>356</v>
       </c>
       <c r="C358" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.15">
@@ -6118,7 +6121,7 @@
         <v>357</v>
       </c>
       <c r="C359" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.15">
@@ -6126,7 +6129,7 @@
         <v>358</v>
       </c>
       <c r="C360" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.15">
@@ -6134,7 +6137,7 @@
         <v>359</v>
       </c>
       <c r="C361" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.15">
@@ -6142,7 +6145,7 @@
         <v>360</v>
       </c>
       <c r="C362" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.15">
@@ -6150,7 +6153,7 @@
         <v>361</v>
       </c>
       <c r="C363" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.15">
@@ -6158,7 +6161,7 @@
         <v>362</v>
       </c>
       <c r="C364" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.15">
@@ -6166,7 +6169,7 @@
         <v>363</v>
       </c>
       <c r="C365" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.15">
@@ -6174,7 +6177,7 @@
         <v>364</v>
       </c>
       <c r="C366" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.15">
@@ -6182,7 +6185,7 @@
         <v>365</v>
       </c>
       <c r="C367" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.15">
@@ -6190,7 +6193,7 @@
         <v>366</v>
       </c>
       <c r="C368" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.15">
@@ -6198,7 +6201,7 @@
         <v>367</v>
       </c>
       <c r="C369" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.15">
@@ -6206,7 +6209,7 @@
         <v>368</v>
       </c>
       <c r="C370" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.15">
@@ -6214,7 +6217,7 @@
         <v>369</v>
       </c>
       <c r="C371" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.15">
@@ -6222,7 +6225,7 @@
         <v>370</v>
       </c>
       <c r="C372" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.15">
@@ -6230,7 +6233,7 @@
         <v>371</v>
       </c>
       <c r="C373" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.15">
@@ -6238,7 +6241,7 @@
         <v>372</v>
       </c>
       <c r="C374" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.15">
@@ -6246,7 +6249,7 @@
         <v>373</v>
       </c>
       <c r="C375" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.15">
@@ -6254,7 +6257,7 @@
         <v>374</v>
       </c>
       <c r="C376" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.15">
@@ -6262,7 +6265,7 @@
         <v>375</v>
       </c>
       <c r="C377" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.15">
@@ -6270,7 +6273,7 @@
         <v>376</v>
       </c>
       <c r="C378" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.15">
@@ -6278,7 +6281,7 @@
         <v>377</v>
       </c>
       <c r="C379" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.15">
@@ -6286,7 +6289,7 @@
         <v>378</v>
       </c>
       <c r="C380" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.15">
@@ -6294,7 +6297,7 @@
         <v>379</v>
       </c>
       <c r="C381" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.15">
@@ -6302,7 +6305,7 @@
         <v>380</v>
       </c>
       <c r="C382" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.15">
@@ -6310,7 +6313,7 @@
         <v>381</v>
       </c>
       <c r="C383" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.15">
@@ -6318,7 +6321,7 @@
         <v>382</v>
       </c>
       <c r="C384" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.15">
@@ -6326,7 +6329,7 @@
         <v>383</v>
       </c>
       <c r="C385" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.15">
@@ -6334,7 +6337,7 @@
         <v>384</v>
       </c>
       <c r="C386" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.15">
@@ -6342,7 +6345,7 @@
         <v>385</v>
       </c>
       <c r="C387" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.15">
@@ -6350,7 +6353,7 @@
         <v>386</v>
       </c>
       <c r="C388" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.15">
@@ -6358,7 +6361,7 @@
         <v>387</v>
       </c>
       <c r="C389" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.15">
@@ -6366,7 +6369,7 @@
         <v>388</v>
       </c>
       <c r="C390" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.15">
@@ -6374,7 +6377,7 @@
         <v>389</v>
       </c>
       <c r="C391" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.15">
@@ -6382,7 +6385,7 @@
         <v>390</v>
       </c>
       <c r="C392" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.15">
@@ -6390,7 +6393,7 @@
         <v>391</v>
       </c>
       <c r="C393" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.15">
@@ -6398,7 +6401,7 @@
         <v>392</v>
       </c>
       <c r="C394" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.15">
@@ -6406,7 +6409,7 @@
         <v>393</v>
       </c>
       <c r="C395" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.15">
@@ -6414,7 +6417,7 @@
         <v>394</v>
       </c>
       <c r="C396" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.15">
@@ -6422,7 +6425,7 @@
         <v>395</v>
       </c>
       <c r="C397" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.15">
@@ -6430,7 +6433,7 @@
         <v>396</v>
       </c>
       <c r="C398" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.15">
@@ -6438,7 +6441,7 @@
         <v>397</v>
       </c>
       <c r="C399" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.15">
@@ -6446,7 +6449,7 @@
         <v>398</v>
       </c>
       <c r="C400" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.15">
@@ -6454,7 +6457,7 @@
         <v>399</v>
       </c>
       <c r="C401" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.15">
@@ -6462,7 +6465,7 @@
         <v>400</v>
       </c>
       <c r="C402" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.15">
@@ -6470,7 +6473,7 @@
         <v>401</v>
       </c>
       <c r="C403" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.15">
@@ -6478,7 +6481,7 @@
         <v>402</v>
       </c>
       <c r="C404" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.15">
@@ -6486,7 +6489,7 @@
         <v>403</v>
       </c>
       <c r="C405" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.15">
@@ -6494,7 +6497,7 @@
         <v>404</v>
       </c>
       <c r="C406" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.15">
@@ -6502,7 +6505,7 @@
         <v>405</v>
       </c>
       <c r="C407" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.15">
@@ -6510,7 +6513,7 @@
         <v>406</v>
       </c>
       <c r="C408" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.15">
@@ -6518,7 +6521,7 @@
         <v>407</v>
       </c>
       <c r="C409" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.15">
@@ -6526,7 +6529,7 @@
         <v>408</v>
       </c>
       <c r="C410" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.15">
@@ -6534,7 +6537,7 @@
         <v>409</v>
       </c>
       <c r="C411" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.15">
@@ -6542,7 +6545,7 @@
         <v>410</v>
       </c>
       <c r="C412" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.15">
@@ -6550,7 +6553,7 @@
         <v>411</v>
       </c>
       <c r="C413" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.15">
@@ -6558,7 +6561,7 @@
         <v>412</v>
       </c>
       <c r="C414" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.15">
@@ -6566,7 +6569,7 @@
         <v>413</v>
       </c>
       <c r="C415" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.15">
@@ -6574,7 +6577,7 @@
         <v>414</v>
       </c>
       <c r="C416" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.15">
@@ -6582,7 +6585,7 @@
         <v>415</v>
       </c>
       <c r="C417" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.15">
@@ -6590,7 +6593,7 @@
         <v>416</v>
       </c>
       <c r="C418" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.15">
@@ -6598,7 +6601,7 @@
         <v>417</v>
       </c>
       <c r="C419" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.15">
@@ -6606,7 +6609,7 @@
         <v>418</v>
       </c>
       <c r="C420" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.15">
@@ -6614,7 +6617,7 @@
         <v>419</v>
       </c>
       <c r="C421" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.15">
@@ -6622,7 +6625,7 @@
         <v>420</v>
       </c>
       <c r="C422" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.15">
@@ -6630,7 +6633,7 @@
         <v>421</v>
       </c>
       <c r="C423" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.15">
@@ -6638,7 +6641,7 @@
         <v>422</v>
       </c>
       <c r="C424" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.15">
@@ -6646,7 +6649,7 @@
         <v>423</v>
       </c>
       <c r="C425" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.15">
@@ -6654,7 +6657,7 @@
         <v>424</v>
       </c>
       <c r="C426" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.15">
@@ -6662,7 +6665,7 @@
         <v>425</v>
       </c>
       <c r="C427" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.15">
@@ -6670,7 +6673,7 @@
         <v>426</v>
       </c>
       <c r="C428" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.15">
@@ -6678,7 +6681,7 @@
         <v>427</v>
       </c>
       <c r="C429" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.15">
@@ -6686,7 +6689,7 @@
         <v>428</v>
       </c>
       <c r="C430" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.15">
@@ -6694,7 +6697,7 @@
         <v>429</v>
       </c>
       <c r="C431" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.15">
@@ -6702,7 +6705,7 @@
         <v>430</v>
       </c>
       <c r="C432" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.15">
@@ -6710,7 +6713,7 @@
         <v>431</v>
       </c>
       <c r="C433" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.15">
@@ -6718,7 +6721,7 @@
         <v>432</v>
       </c>
       <c r="C434" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.15">
@@ -6726,7 +6729,7 @@
         <v>433</v>
       </c>
       <c r="C435" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.15">
@@ -6734,7 +6737,7 @@
         <v>434</v>
       </c>
       <c r="C436" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.15">
@@ -6742,7 +6745,7 @@
         <v>435</v>
       </c>
       <c r="C437" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.15">
@@ -6750,7 +6753,7 @@
         <v>436</v>
       </c>
       <c r="C438" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.15">
@@ -6758,7 +6761,7 @@
         <v>437</v>
       </c>
       <c r="C439" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.15">
@@ -6766,7 +6769,7 @@
         <v>438</v>
       </c>
       <c r="C440" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.15">
@@ -6774,7 +6777,7 @@
         <v>439</v>
       </c>
       <c r="C441" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.15">
@@ -6782,7 +6785,7 @@
         <v>440</v>
       </c>
       <c r="C442" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.15">
@@ -6790,7 +6793,7 @@
         <v>441</v>
       </c>
       <c r="C443" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.15">
@@ -6798,7 +6801,7 @@
         <v>442</v>
       </c>
       <c r="C444" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.15">
@@ -6806,7 +6809,7 @@
         <v>443</v>
       </c>
       <c r="C445" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.15">
@@ -6814,7 +6817,7 @@
         <v>444</v>
       </c>
       <c r="C446" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.15">
@@ -6822,7 +6825,7 @@
         <v>445</v>
       </c>
       <c r="C447" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.15">
@@ -6830,7 +6833,7 @@
         <v>446</v>
       </c>
       <c r="C448" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.15">
@@ -6838,7 +6841,7 @@
         <v>447</v>
       </c>
       <c r="C449" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.15">
@@ -6846,7 +6849,7 @@
         <v>448</v>
       </c>
       <c r="C450" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.15">
@@ -6854,7 +6857,7 @@
         <v>449</v>
       </c>
       <c r="C451" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.15">
@@ -6862,7 +6865,7 @@
         <v>450</v>
       </c>
       <c r="C452" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.15">
@@ -6870,7 +6873,7 @@
         <v>451</v>
       </c>
       <c r="C453" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.15">
@@ -6878,7 +6881,7 @@
         <v>452</v>
       </c>
       <c r="C454" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.15">
@@ -6886,7 +6889,7 @@
         <v>453</v>
       </c>
       <c r="C455" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.15">
@@ -6894,7 +6897,7 @@
         <v>454</v>
       </c>
       <c r="C456" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.15">
@@ -6902,7 +6905,7 @@
         <v>455</v>
       </c>
       <c r="C457" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.15">
@@ -6910,7 +6913,7 @@
         <v>456</v>
       </c>
       <c r="C458" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.15">
@@ -6918,7 +6921,7 @@
         <v>457</v>
       </c>
       <c r="C459" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.15">
@@ -6926,7 +6929,7 @@
         <v>458</v>
       </c>
       <c r="C460" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.15">
@@ -6934,7 +6937,7 @@
         <v>459</v>
       </c>
       <c r="C461" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.15">
@@ -6942,7 +6945,7 @@
         <v>460</v>
       </c>
       <c r="C462" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.15">
@@ -6950,7 +6953,7 @@
         <v>461</v>
       </c>
       <c r="C463" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.15">
@@ -6958,7 +6961,7 @@
         <v>462</v>
       </c>
       <c r="C464" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.15">
@@ -6966,7 +6969,7 @@
         <v>463</v>
       </c>
       <c r="C465" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.15">
@@ -6974,7 +6977,7 @@
         <v>464</v>
       </c>
       <c r="C466" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.15">
@@ -6982,7 +6985,7 @@
         <v>465</v>
       </c>
       <c r="C467" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.15">
@@ -6990,7 +6993,7 @@
         <v>466</v>
       </c>
       <c r="C468" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.15">
@@ -6998,7 +7001,7 @@
         <v>467</v>
       </c>
       <c r="C469" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.15">
@@ -7006,7 +7009,7 @@
         <v>468</v>
       </c>
       <c r="C470" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.15">
@@ -7014,7 +7017,7 @@
         <v>469</v>
       </c>
       <c r="C471" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.15">
@@ -7022,7 +7025,7 @@
         <v>470</v>
       </c>
       <c r="C472" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.15">
@@ -7030,7 +7033,7 @@
         <v>471</v>
       </c>
       <c r="C473" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.15">
@@ -7038,7 +7041,7 @@
         <v>472</v>
       </c>
       <c r="C474" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.15">
@@ -7046,7 +7049,7 @@
         <v>473</v>
       </c>
       <c r="C475" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.15">
@@ -7054,7 +7057,7 @@
         <v>474</v>
       </c>
       <c r="C476" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.15">
@@ -7062,7 +7065,7 @@
         <v>475</v>
       </c>
       <c r="C477" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.15">
@@ -7070,7 +7073,7 @@
         <v>476</v>
       </c>
       <c r="C478" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.15">
@@ -7078,7 +7081,7 @@
         <v>477</v>
       </c>
       <c r="C479" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.15">
@@ -7086,7 +7089,7 @@
         <v>478</v>
       </c>
       <c r="C480" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.15">
@@ -7094,7 +7097,7 @@
         <v>479</v>
       </c>
       <c r="C481" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.15">
@@ -7102,7 +7105,7 @@
         <v>480</v>
       </c>
       <c r="C482" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.15">
@@ -7110,7 +7113,7 @@
         <v>481</v>
       </c>
       <c r="C483" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.15">
@@ -7118,7 +7121,7 @@
         <v>482</v>
       </c>
       <c r="C484" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.15">
@@ -7126,7 +7129,7 @@
         <v>483</v>
       </c>
       <c r="C485" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.15">
@@ -7134,7 +7137,7 @@
         <v>484</v>
       </c>
       <c r="C486" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.15">
@@ -7142,7 +7145,7 @@
         <v>485</v>
       </c>
       <c r="C487" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.15">
@@ -7150,7 +7153,7 @@
         <v>486</v>
       </c>
       <c r="C488" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.15">
@@ -7158,7 +7161,7 @@
         <v>487</v>
       </c>
       <c r="C489" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.15">
@@ -7166,7 +7169,7 @@
         <v>488</v>
       </c>
       <c r="C490" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.15">
@@ -7174,7 +7177,7 @@
         <v>489</v>
       </c>
       <c r="C491" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.15">
@@ -7182,7 +7185,7 @@
         <v>490</v>
       </c>
       <c r="C492" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.15">
@@ -7190,7 +7193,7 @@
         <v>491</v>
       </c>
       <c r="C493" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.15">
@@ -7198,7 +7201,7 @@
         <v>492</v>
       </c>
       <c r="C494" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.15">
@@ -7206,7 +7209,7 @@
         <v>493</v>
       </c>
       <c r="C495" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.15">
@@ -7214,7 +7217,7 @@
         <v>494</v>
       </c>
       <c r="C496" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.15">
@@ -7222,7 +7225,7 @@
         <v>495</v>
       </c>
       <c r="C497" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.15">
@@ -7230,7 +7233,7 @@
         <v>496</v>
       </c>
       <c r="C498" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.15">
@@ -7238,7 +7241,7 @@
         <v>497</v>
       </c>
       <c r="C499" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.15">
@@ -7246,7 +7249,7 @@
         <v>498</v>
       </c>
       <c r="C500" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.15">
@@ -7254,7 +7257,7 @@
         <v>499</v>
       </c>
       <c r="C501" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.15">
@@ -7262,7 +7265,7 @@
         <v>500</v>
       </c>
       <c r="C502" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.15">
@@ -7270,7 +7273,7 @@
         <v>501</v>
       </c>
       <c r="C503" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.15">
@@ -7278,7 +7281,7 @@
         <v>502</v>
       </c>
       <c r="C504" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.15">
@@ -7286,7 +7289,7 @@
         <v>503</v>
       </c>
       <c r="C505" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.15">
@@ -7294,7 +7297,7 @@
         <v>504</v>
       </c>
       <c r="C506" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.15">
@@ -7302,7 +7305,7 @@
         <v>505</v>
       </c>
       <c r="C507" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.15">
@@ -7310,7 +7313,7 @@
         <v>506</v>
       </c>
       <c r="C508" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.15">
@@ -7318,7 +7321,7 @@
         <v>507</v>
       </c>
       <c r="C509" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.15">
@@ -7326,7 +7329,7 @@
         <v>508</v>
       </c>
       <c r="C510" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.15">
@@ -7334,7 +7337,7 @@
         <v>509</v>
       </c>
       <c r="C511" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.15">
@@ -7342,7 +7345,7 @@
         <v>510</v>
       </c>
       <c r="C512" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.15">
@@ -7350,7 +7353,7 @@
         <v>511</v>
       </c>
       <c r="C513" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.15">
@@ -7358,7 +7361,7 @@
         <v>512</v>
       </c>
       <c r="C514" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.15">
@@ -7366,7 +7369,7 @@
         <v>513</v>
       </c>
       <c r="C515" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.15">
@@ -7374,7 +7377,7 @@
         <v>514</v>
       </c>
       <c r="C516" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.15">
@@ -7382,7 +7385,7 @@
         <v>515</v>
       </c>
       <c r="C517" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.15">
@@ -7390,7 +7393,7 @@
         <v>516</v>
       </c>
       <c r="C518" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.15">
@@ -7398,7 +7401,7 @@
         <v>517</v>
       </c>
       <c r="C519" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.15">
@@ -7406,7 +7409,7 @@
         <v>518</v>
       </c>
       <c r="C520" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.15">
@@ -7414,7 +7417,7 @@
         <v>519</v>
       </c>
       <c r="C521" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.15">
@@ -7422,7 +7425,7 @@
         <v>520</v>
       </c>
       <c r="C522" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.15">
@@ -7430,7 +7433,7 @@
         <v>521</v>
       </c>
       <c r="C523" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.15">
@@ -7438,7 +7441,7 @@
         <v>522</v>
       </c>
       <c r="C524" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.15">
@@ -7446,7 +7449,7 @@
         <v>523</v>
       </c>
       <c r="C525" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.15">
@@ -7454,7 +7457,7 @@
         <v>524</v>
       </c>
       <c r="C526" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.15">
@@ -7462,7 +7465,7 @@
         <v>525</v>
       </c>
       <c r="C527" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.15">
@@ -7470,7 +7473,7 @@
         <v>526</v>
       </c>
       <c r="C528" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.15">
@@ -7478,7 +7481,7 @@
         <v>527</v>
       </c>
       <c r="C529" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.15">
@@ -7486,7 +7489,7 @@
         <v>528</v>
       </c>
       <c r="C530" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.15">
@@ -7494,7 +7497,7 @@
         <v>529</v>
       </c>
       <c r="C531" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.15">
@@ -7502,7 +7505,7 @@
         <v>530</v>
       </c>
       <c r="C532" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.15">
@@ -7510,7 +7513,7 @@
         <v>531</v>
       </c>
       <c r="C533" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.15">
@@ -7518,7 +7521,7 @@
         <v>532</v>
       </c>
       <c r="C534" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.15">
@@ -7526,7 +7529,7 @@
         <v>533</v>
       </c>
       <c r="C535" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.15">
@@ -7534,7 +7537,7 @@
         <v>534</v>
       </c>
       <c r="C536" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.15">
@@ -7542,7 +7545,7 @@
         <v>535</v>
       </c>
       <c r="C537" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.15">
@@ -7550,7 +7553,7 @@
         <v>536</v>
       </c>
       <c r="C538" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.15">
@@ -7558,7 +7561,7 @@
         <v>537</v>
       </c>
       <c r="C539" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.15">
@@ -7566,7 +7569,7 @@
         <v>538</v>
       </c>
       <c r="C540" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.15">
@@ -7574,7 +7577,7 @@
         <v>539</v>
       </c>
       <c r="C541" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.15">
@@ -7582,7 +7585,7 @@
         <v>540</v>
       </c>
       <c r="C542" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.15">
@@ -7590,7 +7593,7 @@
         <v>541</v>
       </c>
       <c r="C543" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.15">
@@ -7598,7 +7601,7 @@
         <v>542</v>
       </c>
       <c r="C544" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.15">
@@ -7606,7 +7609,7 @@
         <v>543</v>
       </c>
       <c r="C545" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.15">
@@ -7614,7 +7617,7 @@
         <v>544</v>
       </c>
       <c r="C546" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.15">
@@ -7622,7 +7625,7 @@
         <v>545</v>
       </c>
       <c r="C547" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.15">
@@ -7630,7 +7633,7 @@
         <v>546</v>
       </c>
       <c r="C548" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.15">
@@ -7638,7 +7641,7 @@
         <v>547</v>
       </c>
       <c r="C549" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.15">
@@ -7646,7 +7649,7 @@
         <v>548</v>
       </c>
       <c r="C550" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.15">
@@ -7654,7 +7657,7 @@
         <v>549</v>
       </c>
       <c r="C551" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.15">
@@ -7662,7 +7665,7 @@
         <v>550</v>
       </c>
       <c r="C552" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.15">
@@ -7670,7 +7673,7 @@
         <v>551</v>
       </c>
       <c r="C553" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.15">
@@ -7678,7 +7681,7 @@
         <v>552</v>
       </c>
       <c r="C554" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.15">
@@ -7686,7 +7689,7 @@
         <v>553</v>
       </c>
       <c r="C555" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.15">
@@ -7694,7 +7697,7 @@
         <v>554</v>
       </c>
       <c r="C556" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.15">
@@ -7702,7 +7705,7 @@
         <v>555</v>
       </c>
       <c r="C557" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.15">
@@ -7710,7 +7713,7 @@
         <v>556</v>
       </c>
       <c r="C558" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.15">
@@ -7718,7 +7721,7 @@
         <v>557</v>
       </c>
       <c r="C559" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.15">
@@ -7726,7 +7729,7 @@
         <v>558</v>
       </c>
       <c r="C560" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.15">
@@ -7734,7 +7737,7 @@
         <v>559</v>
       </c>
       <c r="C561" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.15">
@@ -7742,7 +7745,7 @@
         <v>560</v>
       </c>
       <c r="C562" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.15">
@@ -7750,7 +7753,7 @@
         <v>561</v>
       </c>
       <c r="C563" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.15">
@@ -7758,7 +7761,7 @@
         <v>562</v>
       </c>
       <c r="C564" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.15">
@@ -7766,7 +7769,7 @@
         <v>563</v>
       </c>
       <c r="C565" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.15">
@@ -7774,7 +7777,7 @@
         <v>564</v>
       </c>
       <c r="C566" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.15">
@@ -7782,7 +7785,7 @@
         <v>565</v>
       </c>
       <c r="C567" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.15">
@@ -7790,7 +7793,7 @@
         <v>566</v>
       </c>
       <c r="C568" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.15">
@@ -7798,7 +7801,7 @@
         <v>567</v>
       </c>
       <c r="C569" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.15">
@@ -7806,7 +7809,7 @@
         <v>568</v>
       </c>
       <c r="C570" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.15">
@@ -7814,7 +7817,7 @@
         <v>569</v>
       </c>
       <c r="C571" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.15">
@@ -7822,7 +7825,7 @@
         <v>570</v>
       </c>
       <c r="C572" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.15">
@@ -7830,7 +7833,7 @@
         <v>571</v>
       </c>
       <c r="C573" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.15">
@@ -7838,7 +7841,7 @@
         <v>572</v>
       </c>
       <c r="C574" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.15">
@@ -7846,7 +7849,7 @@
         <v>573</v>
       </c>
       <c r="C575" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.15">
@@ -7854,7 +7857,7 @@
         <v>574</v>
       </c>
       <c r="C576" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.15">
@@ -7862,7 +7865,7 @@
         <v>575</v>
       </c>
       <c r="C577" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.15">
@@ -7870,7 +7873,7 @@
         <v>576</v>
       </c>
       <c r="C578" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.15">
@@ -7878,7 +7881,7 @@
         <v>577</v>
       </c>
       <c r="C579" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.15">
@@ -7886,7 +7889,7 @@
         <v>578</v>
       </c>
       <c r="C580" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.15">
@@ -7894,7 +7897,7 @@
         <v>579</v>
       </c>
       <c r="C581" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.15">
@@ -7902,7 +7905,7 @@
         <v>580</v>
       </c>
       <c r="C582" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.15">
@@ -7910,7 +7913,7 @@
         <v>581</v>
       </c>
       <c r="C583" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.15">
@@ -7918,7 +7921,7 @@
         <v>582</v>
       </c>
       <c r="C584" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.15">
@@ -7926,7 +7929,7 @@
         <v>583</v>
       </c>
       <c r="C585" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.15">
@@ -7934,7 +7937,7 @@
         <v>584</v>
       </c>
       <c r="C586" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.15">
@@ -7942,7 +7945,7 @@
         <v>585</v>
       </c>
       <c r="C587" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.15">
@@ -7950,7 +7953,7 @@
         <v>586</v>
       </c>
       <c r="C588" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.15">
@@ -7958,7 +7961,7 @@
         <v>587</v>
       </c>
       <c r="C589" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.15">
@@ -7966,7 +7969,7 @@
         <v>588</v>
       </c>
       <c r="C590" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.15">
@@ -7974,7 +7977,7 @@
         <v>589</v>
       </c>
       <c r="C591" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.15">
@@ -7982,7 +7985,7 @@
         <v>590</v>
       </c>
       <c r="C592" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.15">
@@ -7990,7 +7993,7 @@
         <v>591</v>
       </c>
       <c r="C593" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.15">
@@ -7998,7 +8001,7 @@
         <v>592</v>
       </c>
       <c r="C594" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.15">
@@ -8006,7 +8009,7 @@
         <v>593</v>
       </c>
       <c r="C595" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.15">
@@ -8014,7 +8017,7 @@
         <v>594</v>
       </c>
       <c r="C596" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.15">
@@ -8022,7 +8025,7 @@
         <v>595</v>
       </c>
       <c r="C597" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.15">
@@ -8030,7 +8033,7 @@
         <v>596</v>
       </c>
       <c r="C598" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.15">
@@ -8038,7 +8041,7 @@
         <v>597</v>
       </c>
       <c r="C599" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.15">
@@ -8046,7 +8049,7 @@
         <v>598</v>
       </c>
       <c r="C600" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.15">
@@ -8054,7 +8057,7 @@
         <v>599</v>
       </c>
       <c r="C601" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.15">
@@ -8062,7 +8065,7 @@
         <v>600</v>
       </c>
       <c r="C602" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.15">
@@ -8070,7 +8073,7 @@
         <v>601</v>
       </c>
       <c r="C603" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.15">
@@ -8078,7 +8081,7 @@
         <v>602</v>
       </c>
       <c r="C604" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.15">
@@ -8086,7 +8089,7 @@
         <v>603</v>
       </c>
       <c r="C605" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.15">
@@ -8094,7 +8097,7 @@
         <v>604</v>
       </c>
       <c r="C606" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.15">
@@ -8102,7 +8105,7 @@
         <v>605</v>
       </c>
       <c r="C607" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.15">
@@ -8110,7 +8113,7 @@
         <v>606</v>
       </c>
       <c r="C608" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.15">
@@ -8118,7 +8121,7 @@
         <v>607</v>
       </c>
       <c r="C609" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.15">
@@ -8126,7 +8129,7 @@
         <v>608</v>
       </c>
       <c r="C610" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.15">
@@ -8134,7 +8137,7 @@
         <v>609</v>
       </c>
       <c r="C611" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.15">
@@ -8142,7 +8145,7 @@
         <v>610</v>
       </c>
       <c r="C612" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.15">
@@ -8150,7 +8153,7 @@
         <v>611</v>
       </c>
       <c r="C613" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.15">
@@ -8158,7 +8161,7 @@
         <v>612</v>
       </c>
       <c r="C614" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.15">
@@ -8166,7 +8169,7 @@
         <v>613</v>
       </c>
       <c r="C615" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.15">
@@ -8174,7 +8177,7 @@
         <v>614</v>
       </c>
       <c r="C616" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.15">
@@ -8182,7 +8185,7 @@
         <v>615</v>
       </c>
       <c r="C617" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.15">
@@ -8190,7 +8193,7 @@
         <v>616</v>
       </c>
       <c r="C618" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.15">
@@ -8198,7 +8201,7 @@
         <v>617</v>
       </c>
       <c r="C619" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.15">
@@ -8206,7 +8209,7 @@
         <v>618</v>
       </c>
       <c r="C620" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.15">
@@ -8214,7 +8217,7 @@
         <v>619</v>
       </c>
       <c r="C621" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.15">
@@ -8222,7 +8225,7 @@
         <v>620</v>
       </c>
       <c r="C622" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.15">
@@ -8230,7 +8233,7 @@
         <v>621</v>
       </c>
       <c r="C623" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.15">
@@ -8238,7 +8241,7 @@
         <v>622</v>
       </c>
       <c r="C624" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.15">
@@ -8246,7 +8249,7 @@
         <v>623</v>
       </c>
       <c r="C625" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.15">
@@ -8254,7 +8257,7 @@
         <v>624</v>
       </c>
       <c r="C626" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.15">
@@ -8262,7 +8265,7 @@
         <v>625</v>
       </c>
       <c r="C627" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.15">
@@ -8270,7 +8273,7 @@
         <v>626</v>
       </c>
       <c r="C628" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.15">
@@ -8278,7 +8281,7 @@
         <v>627</v>
       </c>
       <c r="C629" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.15">
@@ -8286,7 +8289,7 @@
         <v>628</v>
       </c>
       <c r="C630" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.15">
@@ -8294,7 +8297,7 @@
         <v>629</v>
       </c>
       <c r="C631" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.15">
@@ -8302,7 +8305,7 @@
         <v>630</v>
       </c>
       <c r="C632" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.15">
@@ -8310,7 +8313,7 @@
         <v>631</v>
       </c>
       <c r="C633" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.15">
@@ -8318,7 +8321,7 @@
         <v>632</v>
       </c>
       <c r="C634" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.15">
@@ -8326,7 +8329,7 @@
         <v>633</v>
       </c>
       <c r="C635" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.15">
@@ -8334,7 +8337,7 @@
         <v>634</v>
       </c>
       <c r="C636" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.15">
@@ -8342,7 +8345,7 @@
         <v>635</v>
       </c>
       <c r="C637" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.15">
@@ -8350,7 +8353,7 @@
         <v>636</v>
       </c>
       <c r="C638" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.15">
@@ -8358,7 +8361,7 @@
         <v>637</v>
       </c>
       <c r="C639" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.15">
@@ -8366,7 +8369,7 @@
         <v>638</v>
       </c>
       <c r="C640" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.15">
@@ -8374,7 +8377,7 @@
         <v>639</v>
       </c>
       <c r="C641" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.15">
@@ -8382,7 +8385,7 @@
         <v>640</v>
       </c>
       <c r="C642" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.15">
@@ -8390,7 +8393,7 @@
         <v>641</v>
       </c>
       <c r="C643" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.15">
@@ -8398,7 +8401,7 @@
         <v>642</v>
       </c>
       <c r="C644" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.15">
@@ -8406,7 +8409,7 @@
         <v>643</v>
       </c>
       <c r="C645" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.15">
@@ -8414,7 +8417,7 @@
         <v>644</v>
       </c>
       <c r="C646" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.15">
@@ -8422,7 +8425,7 @@
         <v>645</v>
       </c>
       <c r="C647" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.15">
@@ -8430,7 +8433,7 @@
         <v>646</v>
       </c>
       <c r="C648" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.15">
@@ -8438,7 +8441,7 @@
         <v>647</v>
       </c>
       <c r="C649" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.15">
@@ -8446,7 +8449,7 @@
         <v>648</v>
       </c>
       <c r="C650" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.15">
@@ -8454,7 +8457,7 @@
         <v>649</v>
       </c>
       <c r="C651" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.15">
@@ -8462,7 +8465,7 @@
         <v>650</v>
       </c>
       <c r="C652" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.15">
@@ -8470,7 +8473,7 @@
         <v>651</v>
       </c>
       <c r="C653" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.15">
@@ -8478,7 +8481,7 @@
         <v>652</v>
       </c>
       <c r="C654" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.15">
@@ -8486,7 +8489,7 @@
         <v>653</v>
       </c>
       <c r="C655" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.15">
@@ -8494,7 +8497,7 @@
         <v>654</v>
       </c>
       <c r="C656" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.15">
@@ -8502,7 +8505,7 @@
         <v>655</v>
       </c>
       <c r="C657" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.15">
@@ -8510,7 +8513,7 @@
         <v>656</v>
       </c>
       <c r="C658" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.15">
@@ -8518,7 +8521,7 @@
         <v>657</v>
       </c>
       <c r="C659" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.15">
@@ -8526,7 +8529,7 @@
         <v>658</v>
       </c>
       <c r="C660" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.15">
@@ -8534,7 +8537,7 @@
         <v>659</v>
       </c>
       <c r="C661" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.15">
@@ -8542,7 +8545,7 @@
         <v>660</v>
       </c>
       <c r="C662" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.15">
@@ -8550,7 +8553,7 @@
         <v>661</v>
       </c>
       <c r="C663" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.15">
@@ -8558,7 +8561,7 @@
         <v>662</v>
       </c>
       <c r="C664" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.15">
@@ -8566,7 +8569,7 @@
         <v>663</v>
       </c>
       <c r="C665" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.15">
@@ -8574,7 +8577,7 @@
         <v>664</v>
       </c>
       <c r="C666" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.15">
@@ -8582,7 +8585,7 @@
         <v>665</v>
       </c>
       <c r="C667" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.15">
@@ -8590,7 +8593,7 @@
         <v>666</v>
       </c>
       <c r="C668" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.15">
@@ -8598,7 +8601,7 @@
         <v>667</v>
       </c>
       <c r="C669" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.15">
@@ -8606,7 +8609,7 @@
         <v>668</v>
       </c>
       <c r="C670" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="671" spans="1:3" x14ac:dyDescent="0.15">
@@ -8614,7 +8617,7 @@
         <v>669</v>
       </c>
       <c r="C671" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.15">
@@ -8622,7 +8625,7 @@
         <v>670</v>
       </c>
       <c r="C672" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.15">
@@ -8630,7 +8633,7 @@
         <v>671</v>
       </c>
       <c r="C673" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.15">
@@ -8638,7 +8641,7 @@
         <v>672</v>
       </c>
       <c r="C674" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.15">
@@ -8646,7 +8649,7 @@
         <v>673</v>
       </c>
       <c r="C675" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.15">
@@ -8654,7 +8657,7 @@
         <v>674</v>
       </c>
       <c r="C676" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="677" spans="1:3" x14ac:dyDescent="0.15">
@@ -8662,7 +8665,7 @@
         <v>675</v>
       </c>
       <c r="C677" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="678" spans="1:3" x14ac:dyDescent="0.15">
@@ -8670,7 +8673,7 @@
         <v>676</v>
       </c>
       <c r="C678" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="679" spans="1:3" x14ac:dyDescent="0.15">
@@ -8678,7 +8681,7 @@
         <v>677</v>
       </c>
       <c r="C679" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.15">
@@ -8686,7 +8689,7 @@
         <v>678</v>
       </c>
       <c r="C680" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.15">
@@ -8694,7 +8697,7 @@
         <v>679</v>
       </c>
       <c r="C681" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.15">
@@ -8702,7 +8705,7 @@
         <v>680</v>
       </c>
       <c r="C682" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.15">
@@ -8710,7 +8713,7 @@
         <v>681</v>
       </c>
       <c r="C683" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.15">
@@ -8718,7 +8721,7 @@
         <v>682</v>
       </c>
       <c r="C684" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.15">
@@ -8726,7 +8729,7 @@
         <v>683</v>
       </c>
       <c r="C685" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.15">
@@ -8734,7 +8737,7 @@
         <v>684</v>
       </c>
       <c r="C686" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.15">
@@ -8742,7 +8745,7 @@
         <v>685</v>
       </c>
       <c r="C687" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.15">
@@ -8750,7 +8753,7 @@
         <v>686</v>
       </c>
       <c r="C688" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="689" spans="1:3" x14ac:dyDescent="0.15">
@@ -8758,7 +8761,7 @@
         <v>687</v>
       </c>
       <c r="C689" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.15">
@@ -8766,7 +8769,7 @@
         <v>688</v>
       </c>
       <c r="C690" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.15">
@@ -8774,7 +8777,7 @@
         <v>689</v>
       </c>
       <c r="C691" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.15">
@@ -8782,7 +8785,7 @@
         <v>690</v>
       </c>
       <c r="C692" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.15">
@@ -8790,7 +8793,7 @@
         <v>691</v>
       </c>
       <c r="C693" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.15">
@@ -8798,7 +8801,7 @@
         <v>692</v>
       </c>
       <c r="C694" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.15">
@@ -8806,7 +8809,7 @@
         <v>693</v>
       </c>
       <c r="C695" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.15">
@@ -8814,7 +8817,7 @@
         <v>694</v>
       </c>
       <c r="C696" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.15">
@@ -8822,7 +8825,7 @@
         <v>695</v>
       </c>
       <c r="C697" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.15">
@@ -8830,7 +8833,7 @@
         <v>696</v>
       </c>
       <c r="C698" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.15">
@@ -8838,7 +8841,7 @@
         <v>697</v>
       </c>
       <c r="C699" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.15">
@@ -8846,7 +8849,7 @@
         <v>698</v>
       </c>
       <c r="C700" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.15">
@@ -8854,7 +8857,7 @@
         <v>699</v>
       </c>
       <c r="C701" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.15">
@@ -8862,7 +8865,7 @@
         <v>700</v>
       </c>
       <c r="C702" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.15">
@@ -8870,7 +8873,7 @@
         <v>701</v>
       </c>
       <c r="C703" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.15">
@@ -8878,7 +8881,7 @@
         <v>702</v>
       </c>
       <c r="C704" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.15">
@@ -8886,7 +8889,7 @@
         <v>703</v>
       </c>
       <c r="C705" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.15">
@@ -8894,7 +8897,7 @@
         <v>704</v>
       </c>
       <c r="C706" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="707" spans="1:3" x14ac:dyDescent="0.15">
@@ -8902,7 +8905,7 @@
         <v>705</v>
       </c>
       <c r="C707" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="708" spans="1:3" x14ac:dyDescent="0.15">
@@ -8910,7 +8913,7 @@
         <v>706</v>
       </c>
       <c r="C708" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="709" spans="1:3" x14ac:dyDescent="0.15">
@@ -8918,7 +8921,7 @@
         <v>707</v>
       </c>
       <c r="C709" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="710" spans="1:3" x14ac:dyDescent="0.15">
@@ -8926,7 +8929,7 @@
         <v>708</v>
       </c>
       <c r="C710" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="711" spans="1:3" x14ac:dyDescent="0.15">
@@ -8934,7 +8937,7 @@
         <v>709</v>
       </c>
       <c r="C711" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="712" spans="1:3" x14ac:dyDescent="0.15">
@@ -8942,7 +8945,7 @@
         <v>710</v>
       </c>
       <c r="C712" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="713" spans="1:3" x14ac:dyDescent="0.15">
@@ -8950,7 +8953,7 @@
         <v>711</v>
       </c>
       <c r="C713" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="714" spans="1:3" x14ac:dyDescent="0.15">
@@ -8958,7 +8961,7 @@
         <v>712</v>
       </c>
       <c r="C714" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="715" spans="1:3" x14ac:dyDescent="0.15">
@@ -8966,7 +8969,7 @@
         <v>713</v>
       </c>
       <c r="C715" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.15">
@@ -8974,7 +8977,7 @@
         <v>714</v>
       </c>
       <c r="C716" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.15">
@@ -8982,7 +8985,7 @@
         <v>715</v>
       </c>
       <c r="C717" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="718" spans="1:3" x14ac:dyDescent="0.15">
@@ -8990,7 +8993,7 @@
         <v>716</v>
       </c>
       <c r="C718" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="719" spans="1:3" x14ac:dyDescent="0.15">
@@ -8998,7 +9001,7 @@
         <v>717</v>
       </c>
       <c r="C719" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="720" spans="1:3" x14ac:dyDescent="0.15">
@@ -9006,7 +9009,7 @@
         <v>718</v>
       </c>
       <c r="C720" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="721" spans="1:3" x14ac:dyDescent="0.15">
@@ -9014,7 +9017,7 @@
         <v>719</v>
       </c>
       <c r="C721" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="722" spans="1:3" x14ac:dyDescent="0.15">
@@ -9022,7 +9025,7 @@
         <v>720</v>
       </c>
       <c r="C722" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="723" spans="1:3" x14ac:dyDescent="0.15">
@@ -9030,7 +9033,7 @@
         <v>721</v>
       </c>
       <c r="C723" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="724" spans="1:3" x14ac:dyDescent="0.15">
@@ -9038,7 +9041,7 @@
         <v>722</v>
       </c>
       <c r="C724" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="725" spans="1:3" x14ac:dyDescent="0.15">
@@ -9046,7 +9049,7 @@
         <v>723</v>
       </c>
       <c r="C725" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="726" spans="1:3" x14ac:dyDescent="0.15">
@@ -9054,7 +9057,7 @@
         <v>724</v>
       </c>
       <c r="C726" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.15">
@@ -9062,7 +9065,7 @@
         <v>725</v>
       </c>
       <c r="C727" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.15">
@@ -9070,7 +9073,7 @@
         <v>726</v>
       </c>
       <c r="C728" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="729" spans="1:3" x14ac:dyDescent="0.15">
@@ -9078,7 +9081,7 @@
         <v>727</v>
       </c>
       <c r="C729" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
     </row>
     <row r="730" spans="1:3" x14ac:dyDescent="0.15">
@@ -9086,7 +9089,7 @@
         <v>728</v>
       </c>
       <c r="C730" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="731" spans="1:3" x14ac:dyDescent="0.15">
@@ -9094,7 +9097,7 @@
         <v>729</v>
       </c>
       <c r="C731" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="732" spans="1:3" x14ac:dyDescent="0.15">
@@ -9102,7 +9105,7 @@
         <v>730</v>
       </c>
       <c r="C732" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="733" spans="1:3" x14ac:dyDescent="0.15">
@@ -9110,7 +9113,7 @@
         <v>731</v>
       </c>
       <c r="C733" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="734" spans="1:3" x14ac:dyDescent="0.15">
@@ -9118,7 +9121,7 @@
         <v>732</v>
       </c>
       <c r="C734" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="735" spans="1:3" x14ac:dyDescent="0.15">
@@ -9126,7 +9129,7 @@
         <v>733</v>
       </c>
       <c r="C735" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="736" spans="1:3" x14ac:dyDescent="0.15">
@@ -9134,7 +9137,7 @@
         <v>734</v>
       </c>
       <c r="C736" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="737" spans="1:3" x14ac:dyDescent="0.15">
@@ -9142,7 +9145,7 @@
         <v>735</v>
       </c>
       <c r="C737" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.15">
@@ -9150,7 +9153,7 @@
         <v>736</v>
       </c>
       <c r="C738" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.15">
@@ -9158,7 +9161,7 @@
         <v>737</v>
       </c>
       <c r="C739" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="740" spans="1:3" x14ac:dyDescent="0.15">
@@ -9166,7 +9169,7 @@
         <v>738</v>
       </c>
       <c r="C740" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="741" spans="1:3" x14ac:dyDescent="0.15">
@@ -9174,7 +9177,7 @@
         <v>739</v>
       </c>
       <c r="C741" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="742" spans="1:3" x14ac:dyDescent="0.15">
@@ -9182,7 +9185,7 @@
         <v>740</v>
       </c>
       <c r="C742" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="743" spans="1:3" x14ac:dyDescent="0.15">
@@ -9190,7 +9193,7 @@
         <v>741</v>
       </c>
       <c r="C743" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="744" spans="1:3" x14ac:dyDescent="0.15">
@@ -9198,7 +9201,7 @@
         <v>742</v>
       </c>
       <c r="C744" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="745" spans="1:3" x14ac:dyDescent="0.15">
@@ -9206,7 +9209,7 @@
         <v>743</v>
       </c>
       <c r="C745" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="746" spans="1:3" x14ac:dyDescent="0.15">
@@ -9214,7 +9217,7 @@
         <v>744</v>
       </c>
       <c r="C746" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="747" spans="1:3" x14ac:dyDescent="0.15">
@@ -9222,7 +9225,7 @@
         <v>745</v>
       </c>
       <c r="C747" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="748" spans="1:3" x14ac:dyDescent="0.15">
@@ -9230,7 +9233,7 @@
         <v>746</v>
       </c>
       <c r="C748" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.15">
@@ -9238,7 +9241,7 @@
         <v>747</v>
       </c>
       <c r="C749" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.15">
@@ -9246,7 +9249,7 @@
         <v>748</v>
       </c>
       <c r="C750" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="751" spans="1:3" x14ac:dyDescent="0.15">
@@ -9254,7 +9257,7 @@
         <v>749</v>
       </c>
       <c r="C751" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="752" spans="1:3" x14ac:dyDescent="0.15">
@@ -9262,7 +9265,7 @@
         <v>750</v>
       </c>
       <c r="C752" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="753" spans="1:3" x14ac:dyDescent="0.15">
@@ -9270,7 +9273,7 @@
         <v>751</v>
       </c>
       <c r="C753" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="754" spans="1:3" x14ac:dyDescent="0.15">
@@ -9278,7 +9281,7 @@
         <v>752</v>
       </c>
       <c r="C754" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="755" spans="1:3" x14ac:dyDescent="0.15">
@@ -9286,7 +9289,7 @@
         <v>753</v>
       </c>
       <c r="C755" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="756" spans="1:3" x14ac:dyDescent="0.15">
@@ -9294,7 +9297,7 @@
         <v>754</v>
       </c>
       <c r="C756" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="757" spans="1:3" x14ac:dyDescent="0.15">
@@ -9302,7 +9305,7 @@
         <v>755</v>
       </c>
       <c r="C757" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="758" spans="1:3" x14ac:dyDescent="0.15">
@@ -9310,7 +9313,7 @@
         <v>756</v>
       </c>
       <c r="C758" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="759" spans="1:3" x14ac:dyDescent="0.15">
@@ -9318,7 +9321,7 @@
         <v>757</v>
       </c>
       <c r="C759" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.15">
@@ -9326,7 +9329,7 @@
         <v>758</v>
       </c>
       <c r="C760" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.15">
@@ -9334,7 +9337,7 @@
         <v>759</v>
       </c>
       <c r="C761" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="762" spans="1:3" x14ac:dyDescent="0.15">
@@ -9342,7 +9345,7 @@
         <v>760</v>
       </c>
       <c r="C762" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="763" spans="1:3" x14ac:dyDescent="0.15">
@@ -9350,7 +9353,7 @@
         <v>761</v>
       </c>
       <c r="C763" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="764" spans="1:3" x14ac:dyDescent="0.15">
@@ -9358,7 +9361,7 @@
         <v>762</v>
       </c>
       <c r="C764" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="765" spans="1:3" x14ac:dyDescent="0.15">
@@ -9366,7 +9369,7 @@
         <v>763</v>
       </c>
       <c r="C765" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="766" spans="1:3" x14ac:dyDescent="0.15">
@@ -9374,7 +9377,7 @@
         <v>764</v>
       </c>
       <c r="C766" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="767" spans="1:3" x14ac:dyDescent="0.15">
@@ -9382,7 +9385,7 @@
         <v>765</v>
       </c>
       <c r="C767" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="768" spans="1:3" x14ac:dyDescent="0.15">
@@ -9390,7 +9393,7 @@
         <v>766</v>
       </c>
       <c r="C768" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="769" spans="1:3" x14ac:dyDescent="0.15">
@@ -9398,7 +9401,7 @@
         <v>767</v>
       </c>
       <c r="C769" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="770" spans="1:3" x14ac:dyDescent="0.15">
@@ -9406,7 +9409,7 @@
         <v>768</v>
       </c>
       <c r="C770" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.15">
@@ -9414,7 +9417,7 @@
         <v>769</v>
       </c>
       <c r="C771" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.15">
@@ -9422,7 +9425,7 @@
         <v>770</v>
       </c>
       <c r="C772" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="773" spans="1:3" x14ac:dyDescent="0.15">
@@ -9430,7 +9433,7 @@
         <v>771</v>
       </c>
       <c r="C773" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="774" spans="1:3" x14ac:dyDescent="0.15">
@@ -9438,7 +9441,7 @@
         <v>772</v>
       </c>
       <c r="C774" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="775" spans="1:3" x14ac:dyDescent="0.15">
@@ -9446,7 +9449,7 @@
         <v>773</v>
       </c>
       <c r="C775" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="776" spans="1:3" x14ac:dyDescent="0.15">
@@ -9454,7 +9457,7 @@
         <v>774</v>
       </c>
       <c r="C776" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="777" spans="1:3" x14ac:dyDescent="0.15">
@@ -9462,7 +9465,7 @@
         <v>775</v>
       </c>
       <c r="C777" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="778" spans="1:3" x14ac:dyDescent="0.15">
@@ -9470,7 +9473,7 @@
         <v>776</v>
       </c>
       <c r="C778" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="779" spans="1:3" x14ac:dyDescent="0.15">
@@ -9478,7 +9481,7 @@
         <v>777</v>
       </c>
       <c r="C779" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="780" spans="1:3" x14ac:dyDescent="0.15">
@@ -9486,7 +9489,7 @@
         <v>778</v>
       </c>
       <c r="C780" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="781" spans="1:3" x14ac:dyDescent="0.15">
@@ -9494,7 +9497,7 @@
         <v>779</v>
       </c>
       <c r="C781" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.15">
@@ -9502,7 +9505,7 @@
         <v>780</v>
       </c>
       <c r="C782" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.15">
@@ -9510,7 +9513,7 @@
         <v>781</v>
       </c>
       <c r="C783" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="784" spans="1:3" x14ac:dyDescent="0.15">
@@ -9518,7 +9521,7 @@
         <v>782</v>
       </c>
       <c r="C784" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="785" spans="1:3" x14ac:dyDescent="0.15">
@@ -9526,7 +9529,7 @@
         <v>783</v>
       </c>
       <c r="C785" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="786" spans="1:3" x14ac:dyDescent="0.15">
@@ -9534,7 +9537,7 @@
         <v>784</v>
       </c>
       <c r="C786" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="787" spans="1:3" x14ac:dyDescent="0.15">
@@ -9542,7 +9545,7 @@
         <v>785</v>
       </c>
       <c r="C787" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="788" spans="1:3" x14ac:dyDescent="0.15">
@@ -9550,7 +9553,7 @@
         <v>786</v>
       </c>
       <c r="C788" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="789" spans="1:3" x14ac:dyDescent="0.15">
@@ -9558,7 +9561,7 @@
         <v>787</v>
       </c>
       <c r="C789" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="790" spans="1:3" x14ac:dyDescent="0.15">
@@ -9566,7 +9569,7 @@
         <v>788</v>
       </c>
       <c r="C790" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="791" spans="1:3" x14ac:dyDescent="0.15">
@@ -9574,7 +9577,7 @@
         <v>789</v>
       </c>
       <c r="C791" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="792" spans="1:3" x14ac:dyDescent="0.15">
@@ -9582,7 +9585,7 @@
         <v>790</v>
       </c>
       <c r="C792" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.15">
@@ -9590,7 +9593,7 @@
         <v>791</v>
       </c>
       <c r="C793" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.15">
@@ -9598,7 +9601,7 @@
         <v>792</v>
       </c>
       <c r="C794" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="795" spans="1:3" x14ac:dyDescent="0.15">
@@ -9606,7 +9609,7 @@
         <v>793</v>
       </c>
       <c r="C795" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="796" spans="1:3" x14ac:dyDescent="0.15">
@@ -9614,7 +9617,7 @@
         <v>794</v>
       </c>
       <c r="C796" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="797" spans="1:3" x14ac:dyDescent="0.15">
@@ -9622,7 +9625,7 @@
         <v>795</v>
       </c>
       <c r="C797" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="798" spans="1:3" x14ac:dyDescent="0.15">
@@ -9630,7 +9633,7 @@
         <v>796</v>
       </c>
       <c r="C798" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="799" spans="1:3" x14ac:dyDescent="0.15">
@@ -9638,7 +9641,7 @@
         <v>797</v>
       </c>
       <c r="C799" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="800" spans="1:3" x14ac:dyDescent="0.15">
@@ -9646,7 +9649,7 @@
         <v>798</v>
       </c>
       <c r="C800" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="801" spans="1:3" x14ac:dyDescent="0.15">
@@ -9654,7 +9657,7 @@
         <v>799</v>
       </c>
       <c r="C801" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="802" spans="1:3" x14ac:dyDescent="0.15">
@@ -9662,7 +9665,7 @@
         <v>800</v>
       </c>
       <c r="C802" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="803" spans="1:3" x14ac:dyDescent="0.15">
@@ -9670,7 +9673,7 @@
         <v>801</v>
       </c>
       <c r="C803" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.15">
@@ -9678,7 +9681,7 @@
         <v>802</v>
       </c>
       <c r="C804" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.15">
@@ -9686,7 +9689,7 @@
         <v>803</v>
       </c>
       <c r="C805" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="806" spans="1:3" x14ac:dyDescent="0.15">
@@ -9694,7 +9697,7 @@
         <v>804</v>
       </c>
       <c r="C806" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="807" spans="1:3" x14ac:dyDescent="0.15">
@@ -9702,7 +9705,7 @@
         <v>805</v>
       </c>
       <c r="C807" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="808" spans="1:3" x14ac:dyDescent="0.15">
@@ -9710,7 +9713,7 @@
         <v>806</v>
       </c>
       <c r="C808" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="809" spans="1:3" x14ac:dyDescent="0.15">
@@ -9718,7 +9721,7 @@
         <v>807</v>
       </c>
       <c r="C809" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="810" spans="1:3" x14ac:dyDescent="0.15">
@@ -9726,7 +9729,7 @@
         <v>808</v>
       </c>
       <c r="C810" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="811" spans="1:3" x14ac:dyDescent="0.15">
@@ -9734,7 +9737,7 @@
         <v>809</v>
       </c>
       <c r="C811" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="812" spans="1:3" x14ac:dyDescent="0.15">
@@ -9742,7 +9745,7 @@
         <v>810</v>
       </c>
       <c r="C812" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="813" spans="1:3" x14ac:dyDescent="0.15">
@@ -9750,7 +9753,7 @@
         <v>811</v>
       </c>
       <c r="C813" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="814" spans="1:3" x14ac:dyDescent="0.15">
@@ -9758,7 +9761,7 @@
         <v>812</v>
       </c>
       <c r="C814" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.15">
@@ -9766,7 +9769,7 @@
         <v>813</v>
       </c>
       <c r="C815" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.15">
@@ -9774,7 +9777,7 @@
         <v>814</v>
       </c>
       <c r="C816" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="817" spans="1:3" x14ac:dyDescent="0.15">
@@ -9782,7 +9785,7 @@
         <v>815</v>
       </c>
       <c r="C817" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="818" spans="1:3" x14ac:dyDescent="0.15">
@@ -9790,7 +9793,7 @@
         <v>816</v>
       </c>
       <c r="C818" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="819" spans="1:3" x14ac:dyDescent="0.15">
@@ -9798,7 +9801,7 @@
         <v>817</v>
       </c>
       <c r="C819" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="820" spans="1:3" x14ac:dyDescent="0.15">
@@ -9806,7 +9809,7 @@
         <v>818</v>
       </c>
       <c r="C820" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="821" spans="1:3" x14ac:dyDescent="0.15">
@@ -9814,7 +9817,7 @@
         <v>819</v>
       </c>
       <c r="C821" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="822" spans="1:3" x14ac:dyDescent="0.15">
@@ -9822,7 +9825,7 @@
         <v>820</v>
       </c>
       <c r="C822" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="823" spans="1:3" x14ac:dyDescent="0.15">
@@ -9830,7 +9833,7 @@
         <v>821</v>
       </c>
       <c r="C823" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="824" spans="1:3" x14ac:dyDescent="0.15">
@@ -9838,7 +9841,7 @@
         <v>822</v>
       </c>
       <c r="C824" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="825" spans="1:3" x14ac:dyDescent="0.15">
@@ -9846,7 +9849,7 @@
         <v>823</v>
       </c>
       <c r="C825" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.15">
@@ -9854,7 +9857,7 @@
         <v>824</v>
       </c>
       <c r="C826" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.15">
@@ -9862,7 +9865,7 @@
         <v>825</v>
       </c>
       <c r="C827" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="828" spans="1:3" x14ac:dyDescent="0.15">
@@ -9870,7 +9873,7 @@
         <v>826</v>
       </c>
       <c r="C828" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="829" spans="1:3" x14ac:dyDescent="0.15">
@@ -9878,7 +9881,7 @@
         <v>827</v>
       </c>
       <c r="C829" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="830" spans="1:3" x14ac:dyDescent="0.15">
@@ -9886,7 +9889,7 @@
         <v>828</v>
       </c>
       <c r="C830" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="831" spans="1:3" x14ac:dyDescent="0.15">
@@ -9894,7 +9897,7 @@
         <v>829</v>
       </c>
       <c r="C831" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="832" spans="1:3" x14ac:dyDescent="0.15">
@@ -9902,7 +9905,7 @@
         <v>830</v>
       </c>
       <c r="C832" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="833" spans="1:3" x14ac:dyDescent="0.15">
@@ -9910,7 +9913,7 @@
         <v>831</v>
       </c>
       <c r="C833" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="834" spans="1:3" x14ac:dyDescent="0.15">
@@ -9918,7 +9921,7 @@
         <v>832</v>
       </c>
       <c r="C834" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="835" spans="1:3" x14ac:dyDescent="0.15">
@@ -9926,7 +9929,7 @@
         <v>833</v>
       </c>
       <c r="C835" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="836" spans="1:3" x14ac:dyDescent="0.15">
@@ -9934,7 +9937,7 @@
         <v>834</v>
       </c>
       <c r="C836" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.15">
@@ -9942,7 +9945,7 @@
         <v>835</v>
       </c>
       <c r="C837" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.15">
@@ -9950,7 +9953,7 @@
         <v>836</v>
       </c>
       <c r="C838" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="839" spans="1:3" x14ac:dyDescent="0.15">
@@ -9958,7 +9961,7 @@
         <v>837</v>
       </c>
       <c r="C839" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="840" spans="1:3" x14ac:dyDescent="0.15">
@@ -9966,7 +9969,7 @@
         <v>838</v>
       </c>
       <c r="C840" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="841" spans="1:3" x14ac:dyDescent="0.15">
@@ -9974,7 +9977,7 @@
         <v>839</v>
       </c>
       <c r="C841" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="842" spans="1:3" x14ac:dyDescent="0.15">
@@ -9982,7 +9985,7 @@
         <v>840</v>
       </c>
       <c r="C842" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="843" spans="1:3" x14ac:dyDescent="0.15">
@@ -9990,7 +9993,7 @@
         <v>841</v>
       </c>
       <c r="C843" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="844" spans="1:3" x14ac:dyDescent="0.15">
@@ -9998,7 +10001,7 @@
         <v>842</v>
       </c>
       <c r="C844" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="845" spans="1:3" x14ac:dyDescent="0.15">
@@ -10006,7 +10009,7 @@
         <v>843</v>
       </c>
       <c r="C845" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="846" spans="1:3" x14ac:dyDescent="0.15">
@@ -10014,7 +10017,7 @@
         <v>844</v>
       </c>
       <c r="C846" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="847" spans="1:3" x14ac:dyDescent="0.15">
@@ -10022,7 +10025,7 @@
         <v>845</v>
       </c>
       <c r="C847" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.15">
@@ -10030,7 +10033,7 @@
         <v>846</v>
       </c>
       <c r="C848" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.15">
@@ -10038,7 +10041,7 @@
         <v>847</v>
       </c>
       <c r="C849" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="850" spans="1:3" x14ac:dyDescent="0.15">
@@ -10046,7 +10049,7 @@
         <v>848</v>
       </c>
       <c r="C850" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="851" spans="1:3" x14ac:dyDescent="0.15">
@@ -10054,7 +10057,7 @@
         <v>849</v>
       </c>
       <c r="C851" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="852" spans="1:3" x14ac:dyDescent="0.15">
@@ -10062,7 +10065,7 @@
         <v>850</v>
       </c>
       <c r="C852" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="853" spans="1:3" x14ac:dyDescent="0.15">
@@ -10070,7 +10073,7 @@
         <v>851</v>
       </c>
       <c r="C853" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="854" spans="1:3" x14ac:dyDescent="0.15">
@@ -10078,7 +10081,7 @@
         <v>852</v>
       </c>
       <c r="C854" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="855" spans="1:3" x14ac:dyDescent="0.15">
@@ -10086,7 +10089,7 @@
         <v>853</v>
       </c>
       <c r="C855" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="856" spans="1:3" x14ac:dyDescent="0.15">
@@ -10094,7 +10097,7 @@
         <v>854</v>
       </c>
       <c r="C856" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="857" spans="1:3" x14ac:dyDescent="0.15">
@@ -10102,7 +10105,7 @@
         <v>855</v>
       </c>
       <c r="C857" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="858" spans="1:3" x14ac:dyDescent="0.15">
@@ -10110,7 +10113,7 @@
         <v>856</v>
       </c>
       <c r="C858" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.15">
@@ -10118,7 +10121,7 @@
         <v>857</v>
       </c>
       <c r="C859" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.15">
@@ -10126,7 +10129,7 @@
         <v>858</v>
       </c>
       <c r="C860" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="861" spans="1:3" x14ac:dyDescent="0.15">
@@ -10134,7 +10137,7 @@
         <v>859</v>
       </c>
       <c r="C861" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="862" spans="1:3" x14ac:dyDescent="0.15">
@@ -10142,7 +10145,7 @@
         <v>860</v>
       </c>
       <c r="C862" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="863" spans="1:3" x14ac:dyDescent="0.15">
@@ -10150,7 +10153,7 @@
         <v>861</v>
       </c>
       <c r="C863" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="864" spans="1:3" x14ac:dyDescent="0.15">
@@ -10158,7 +10161,7 @@
         <v>862</v>
       </c>
       <c r="C864" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="865" spans="1:3" x14ac:dyDescent="0.15">
@@ -10166,7 +10169,7 @@
         <v>863</v>
       </c>
       <c r="C865" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="866" spans="1:3" x14ac:dyDescent="0.15">
@@ -10174,7 +10177,7 @@
         <v>864</v>
       </c>
       <c r="C866" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="867" spans="1:3" x14ac:dyDescent="0.15">
@@ -10182,7 +10185,7 @@
         <v>865</v>
       </c>
       <c r="C867" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="868" spans="1:3" x14ac:dyDescent="0.15">
@@ -10190,7 +10193,7 @@
         <v>866</v>
       </c>
       <c r="C868" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="869" spans="1:3" x14ac:dyDescent="0.15">
@@ -10198,7 +10201,7 @@
         <v>867</v>
       </c>
       <c r="C869" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.15">
@@ -10206,7 +10209,7 @@
         <v>868</v>
       </c>
       <c r="C870" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.15">
@@ -10214,7 +10217,7 @@
         <v>869</v>
       </c>
       <c r="C871" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="872" spans="1:3" x14ac:dyDescent="0.15">
@@ -10222,7 +10225,7 @@
         <v>870</v>
       </c>
       <c r="C872" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="873" spans="1:3" x14ac:dyDescent="0.15">
@@ -10230,7 +10233,7 @@
         <v>871</v>
       </c>
       <c r="C873" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="874" spans="1:3" x14ac:dyDescent="0.15">
@@ -10238,7 +10241,7 @@
         <v>872</v>
       </c>
       <c r="C874" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="875" spans="1:3" x14ac:dyDescent="0.15">
@@ -10246,7 +10249,7 @@
         <v>873</v>
       </c>
       <c r="C875" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="876" spans="1:3" x14ac:dyDescent="0.15">
@@ -10254,7 +10257,7 @@
         <v>874</v>
       </c>
       <c r="C876" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="877" spans="1:3" x14ac:dyDescent="0.15">
@@ -10262,7 +10265,7 @@
         <v>875</v>
       </c>
       <c r="C877" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="878" spans="1:3" x14ac:dyDescent="0.15">
@@ -10270,7 +10273,7 @@
         <v>876</v>
       </c>
       <c r="C878" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="879" spans="1:3" x14ac:dyDescent="0.15">
@@ -10278,7 +10281,7 @@
         <v>877</v>
       </c>
       <c r="C879" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="880" spans="1:3" x14ac:dyDescent="0.15">
@@ -10286,7 +10289,7 @@
         <v>878</v>
       </c>
       <c r="C880" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.15">
@@ -10294,7 +10297,7 @@
         <v>879</v>
       </c>
       <c r="C881" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.15">
@@ -10302,7 +10305,7 @@
         <v>880</v>
       </c>
       <c r="C882" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="883" spans="1:3" x14ac:dyDescent="0.15">
@@ -10310,7 +10313,7 @@
         <v>881</v>
       </c>
       <c r="C883" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="884" spans="1:3" x14ac:dyDescent="0.15">
@@ -10318,7 +10321,7 @@
         <v>882</v>
       </c>
       <c r="C884" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="885" spans="1:3" x14ac:dyDescent="0.15">
@@ -10326,7 +10329,7 @@
         <v>883</v>
       </c>
       <c r="C885" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="886" spans="1:3" x14ac:dyDescent="0.15">
@@ -10334,7 +10337,7 @@
         <v>884</v>
       </c>
       <c r="C886" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="887" spans="1:3" x14ac:dyDescent="0.15">
@@ -10342,7 +10345,7 @@
         <v>885</v>
       </c>
       <c r="C887" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="888" spans="1:3" x14ac:dyDescent="0.15">
@@ -10350,7 +10353,7 @@
         <v>886</v>
       </c>
       <c r="C888" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="889" spans="1:3" x14ac:dyDescent="0.15">
@@ -10358,7 +10361,7 @@
         <v>887</v>
       </c>
       <c r="C889" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="890" spans="1:3" x14ac:dyDescent="0.15">
@@ -10366,7 +10369,7 @@
         <v>888</v>
       </c>
       <c r="C890" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="891" spans="1:3" x14ac:dyDescent="0.15">
@@ -10374,7 +10377,7 @@
         <v>889</v>
       </c>
       <c r="C891" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.15">
@@ -10382,7 +10385,7 @@
         <v>890</v>
       </c>
       <c r="C892" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.15">
@@ -10390,7 +10393,7 @@
         <v>891</v>
       </c>
       <c r="C893" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="894" spans="1:3" x14ac:dyDescent="0.15">
@@ -10398,7 +10401,7 @@
         <v>892</v>
       </c>
       <c r="C894" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="895" spans="1:3" x14ac:dyDescent="0.15">
@@ -10406,7 +10409,7 @@
         <v>893</v>
       </c>
       <c r="C895" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="896" spans="1:3" x14ac:dyDescent="0.15">
@@ -10414,7 +10417,7 @@
         <v>894</v>
       </c>
       <c r="C896" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="897" spans="1:3" x14ac:dyDescent="0.15">
@@ -10422,7 +10425,7 @@
         <v>895</v>
       </c>
       <c r="C897" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="898" spans="1:3" x14ac:dyDescent="0.15">
@@ -10430,7 +10433,7 @@
         <v>896</v>
       </c>
       <c r="C898" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="899" spans="1:3" x14ac:dyDescent="0.15">
@@ -10438,7 +10441,7 @@
         <v>897</v>
       </c>
       <c r="C899" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="900" spans="1:3" x14ac:dyDescent="0.15">
@@ -10446,7 +10449,7 @@
         <v>898</v>
       </c>
       <c r="C900" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="901" spans="1:3" x14ac:dyDescent="0.15">
@@ -10454,7 +10457,7 @@
         <v>899</v>
       </c>
       <c r="C901" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="902" spans="1:3" x14ac:dyDescent="0.15">
@@ -10462,7 +10465,7 @@
         <v>900</v>
       </c>
       <c r="C902" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.15">
@@ -10470,7 +10473,7 @@
         <v>901</v>
       </c>
       <c r="C903" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.15">
@@ -10478,7 +10481,7 @@
         <v>902</v>
       </c>
       <c r="C904" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="905" spans="1:3" x14ac:dyDescent="0.15">
@@ -10486,7 +10489,7 @@
         <v>903</v>
       </c>
       <c r="C905" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="906" spans="1:3" x14ac:dyDescent="0.15">
@@ -10494,7 +10497,7 @@
         <v>904</v>
       </c>
       <c r="C906" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="907" spans="1:3" x14ac:dyDescent="0.15">
@@ -10502,7 +10505,7 @@
         <v>905</v>
       </c>
       <c r="C907" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="908" spans="1:3" x14ac:dyDescent="0.15">
@@ -10510,7 +10513,7 @@
         <v>906</v>
       </c>
       <c r="C908" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="909" spans="1:3" x14ac:dyDescent="0.15">
@@ -10518,7 +10521,7 @@
         <v>907</v>
       </c>
       <c r="C909" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="910" spans="1:3" x14ac:dyDescent="0.15">
@@ -10526,7 +10529,7 @@
         <v>908</v>
       </c>
       <c r="C910" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="911" spans="1:3" x14ac:dyDescent="0.15">
@@ -10534,7 +10537,7 @@
         <v>909</v>
       </c>
       <c r="C911" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="912" spans="1:3" x14ac:dyDescent="0.15">
@@ -10542,7 +10545,7 @@
         <v>910</v>
       </c>
       <c r="C912" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="913" spans="1:3" x14ac:dyDescent="0.15">
@@ -10550,7 +10553,7 @@
         <v>911</v>
       </c>
       <c r="C913" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.15">
@@ -10558,7 +10561,7 @@
         <v>912</v>
       </c>
       <c r="C914" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.15">
@@ -10566,7 +10569,7 @@
         <v>913</v>
       </c>
       <c r="C915" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="916" spans="1:3" x14ac:dyDescent="0.15">
@@ -10574,7 +10577,7 @@
         <v>914</v>
       </c>
       <c r="C916" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="917" spans="1:3" x14ac:dyDescent="0.15">
@@ -10582,7 +10585,7 @@
         <v>915</v>
       </c>
       <c r="C917" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="918" spans="1:3" x14ac:dyDescent="0.15">
@@ -10590,7 +10593,7 @@
         <v>916</v>
       </c>
       <c r="C918" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="919" spans="1:3" x14ac:dyDescent="0.15">
@@ -10598,7 +10601,7 @@
         <v>917</v>
       </c>
       <c r="C919" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="920" spans="1:3" x14ac:dyDescent="0.15">
@@ -10606,7 +10609,7 @@
         <v>918</v>
       </c>
       <c r="C920" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="921" spans="1:3" x14ac:dyDescent="0.15">
@@ -10614,7 +10617,7 @@
         <v>919</v>
       </c>
       <c r="C921" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="922" spans="1:3" x14ac:dyDescent="0.15">
@@ -10622,7 +10625,7 @@
         <v>920</v>
       </c>
       <c r="C922" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="923" spans="1:3" x14ac:dyDescent="0.15">
@@ -10630,7 +10633,7 @@
         <v>921</v>
       </c>
       <c r="C923" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="924" spans="1:3" x14ac:dyDescent="0.15">
@@ -10638,7 +10641,7 @@
         <v>922</v>
       </c>
       <c r="C924" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.15">
@@ -10646,7 +10649,7 @@
         <v>923</v>
       </c>
       <c r="C925" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.15">
@@ -10654,7 +10657,7 @@
         <v>924</v>
       </c>
       <c r="C926" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="927" spans="1:3" x14ac:dyDescent="0.15">
@@ -10662,7 +10665,7 @@
         <v>925</v>
       </c>
       <c r="C927" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="928" spans="1:3" x14ac:dyDescent="0.15">
@@ -10670,7 +10673,7 @@
         <v>926</v>
       </c>
       <c r="C928" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="929" spans="1:3" x14ac:dyDescent="0.15">
@@ -10678,7 +10681,7 @@
         <v>927</v>
       </c>
       <c r="C929" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="930" spans="1:3" x14ac:dyDescent="0.15">
@@ -10686,7 +10689,7 @@
         <v>928</v>
       </c>
       <c r="C930" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="931" spans="1:3" x14ac:dyDescent="0.15">
@@ -10694,7 +10697,7 @@
         <v>929</v>
       </c>
       <c r="C931" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="932" spans="1:3" x14ac:dyDescent="0.15">
@@ -10702,7 +10705,7 @@
         <v>930</v>
       </c>
       <c r="C932" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="933" spans="1:3" x14ac:dyDescent="0.15">
@@ -10710,7 +10713,7 @@
         <v>931</v>
       </c>
       <c r="C933" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="934" spans="1:3" x14ac:dyDescent="0.15">
@@ -10718,7 +10721,7 @@
         <v>932</v>
       </c>
       <c r="C934" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="935" spans="1:3" x14ac:dyDescent="0.15">
@@ -10726,7 +10729,7 @@
         <v>933</v>
       </c>
       <c r="C935" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.15">
@@ -10734,7 +10737,7 @@
         <v>934</v>
       </c>
       <c r="C936" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.15">
@@ -10742,7 +10745,7 @@
         <v>935</v>
       </c>
       <c r="C937" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="938" spans="1:3" x14ac:dyDescent="0.15">
@@ -10750,7 +10753,7 @@
         <v>936</v>
       </c>
       <c r="C938" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="939" spans="1:3" x14ac:dyDescent="0.15">
@@ -10758,7 +10761,7 @@
         <v>937</v>
       </c>
       <c r="C939" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="940" spans="1:3" x14ac:dyDescent="0.15">
@@ -10766,7 +10769,7 @@
         <v>938</v>
       </c>
       <c r="C940" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="941" spans="1:3" x14ac:dyDescent="0.15">
@@ -10774,7 +10777,7 @@
         <v>939</v>
       </c>
       <c r="C941" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="942" spans="1:3" x14ac:dyDescent="0.15">
@@ -10782,7 +10785,7 @@
         <v>940</v>
       </c>
       <c r="C942" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="943" spans="1:3" x14ac:dyDescent="0.15">
@@ -10790,7 +10793,7 @@
         <v>941</v>
       </c>
       <c r="C943" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
   </sheetData>
